--- a/Fonds-Compagnies-Suivi_MODELE_CDR_TO.xlsx
+++ b/Fonds-Compagnies-Suivi_MODELE_CDR_TO.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\_ChatGPT_Fonds_Compagnies_Analyse\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92166DF7-7D93-41B7-891F-4D51857E33C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DEAD1A97-E936-4A51-997A-837E2CF180EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="YF_Data" sheetId="2" r:id="rId2"/>
     <sheet name="ETAPES" sheetId="3" r:id="rId3"/>
     <sheet name="Règles d'Investissement" sheetId="4" r:id="rId4"/>
-    <sheet name="Contrôle-Pertes-Capital" sheetId="6" r:id="rId5"/>
+    <sheet name="Contrôle-Pertes-Capital" sheetId="5" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="4">'Contrôle-Pertes-Capital'!$A$1:$K$25</definedName>
@@ -36,12 +36,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="145">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="148">
   <si>
     <t>Date mise à jour (script ChatGPT) :</t>
-  </si>
-  <si>
-    <t>2026-01-27</t>
   </si>
   <si>
     <t>Description-Fonds-Actions</t>
@@ -69,38 +66,90 @@
 [VUG, VGT, IYW, QQQ]</t>
   </si>
   <si>
+    <t xml:space="preserve">DIVIDENDE
+(VIC200, VGG, RBF902)
+(VDY, RBF646, FID2930)
+ [VYM, VIG, SCHD] 
+</t>
+  </si>
+  <si>
+    <t>OR 
+(Indice métal)
+(CGL.TO, PHYS.TO)
+[IAU]</t>
+  </si>
+  <si>
+    <t>CHIPS
+(XCHP.TO, CHPS.TO)
+[SOXX, SMH]</t>
+  </si>
+  <si>
     <t>Nvidia
 (nvda.cdr)</t>
   </si>
   <si>
+    <t>Broadcom
+(avgo.cdr)</t>
+  </si>
+  <si>
+    <t>Apple
+(aapl.cdr)</t>
+  </si>
+  <si>
     <t>Google
 (goog.cdr)</t>
   </si>
   <si>
-    <t>Apple
-(aapl.cdr)</t>
-  </si>
-  <si>
-    <t>Broadcom
-(avgo.cdr)</t>
-  </si>
-  <si>
     <t>Oracle
 (orac.cdr)</t>
   </si>
   <si>
+    <t>Vernova
+(gev.cdr)</t>
+  </si>
+  <si>
     <t>Tickers (Codes)</t>
   </si>
   <si>
     <t>XWD.TO</t>
   </si>
   <si>
+    <t>VUN.TO</t>
+  </si>
+  <si>
     <t>XSP.TO</t>
   </si>
   <si>
     <t>XQQ.TO</t>
   </si>
   <si>
+    <t>VGG.TO</t>
+  </si>
+  <si>
+    <t>CGL.TO</t>
+  </si>
+  <si>
+    <t>XCHP.TO</t>
+  </si>
+  <si>
+    <t>NVDA.TO</t>
+  </si>
+  <si>
+    <t>AVGO.TO</t>
+  </si>
+  <si>
+    <t>AAPL.TO</t>
+  </si>
+  <si>
+    <t>GOOG.TO</t>
+  </si>
+  <si>
+    <t>ORAC.TO</t>
+  </si>
+  <si>
+    <t>GEV.TO</t>
+  </si>
+  <si>
     <t>Valeur (prix actuel, $)</t>
   </si>
   <si>
@@ -146,13 +195,7 @@
     <t>Notation des analystes (Yahoo)</t>
   </si>
   <si>
-    <t>Strong_Buy</t>
-  </si>
-  <si>
-    <t>Buy</t>
-  </si>
-  <si>
-    <t>Hold</t>
+    <t>None</t>
   </si>
   <si>
     <t>Niveau de Risque</t>
@@ -164,392 +207,6 @@
     <t>Élevé</t>
   </si>
   <si>
-    <t>Ticker</t>
-  </si>
-  <si>
-    <t>Objectif: Mise à jour 1-Clic via Python (YFinance).</t>
-  </si>
-  <si>
-    <t>1) Copier les 4 fichiers dans le même répertoire :</t>
-  </si>
-  <si>
-    <t xml:space="preserve">   - Fichier Excel (MODELE.xlsx)</t>
-  </si>
-  <si>
-    <t>3) Installer les dépendances (une (1) seule fois) :</t>
-  </si>
-  <si>
-    <t xml:space="preserve">   - Ouvrir une Invite de commandes dans ce dossier.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">   - Taper :</t>
-  </si>
-  <si>
-    <t>4) Mettre à jour :</t>
-  </si>
-  <si>
-    <t xml:space="preserve">   - Fermer Excel (important).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">   - Un fichier *_MAJ.xlsx est créé + un *_LOG.txt.</t>
-  </si>
-  <si>
-    <t>5) Personnaliser (si besoin) :</t>
-  </si>
-  <si>
-    <t xml:space="preserve">   - Modifie les tickers sur la ligne 3 (B→...). Le script suivra automatiquement.</t>
-  </si>
-  <si>
-    <t>* Règles d'Investissement</t>
-  </si>
-  <si>
-    <t>* "Les rendements antérieurs ne se répètent pas nécessairement".</t>
-  </si>
-  <si>
-    <t>* Regarder principalement le rendement sur 10 ans (les fonds indiciels en priorité).</t>
-  </si>
-  <si>
-    <t>* Prendre avec prudence les rendements trop élevés (&gt;30%, pas de garantie).</t>
-  </si>
-  <si>
-    <t>* S'assurer qu'on peut tolérer le niveau de risque associé à un fonds ou à l'action d'une compagnie.</t>
-  </si>
-  <si>
-    <t>* Faire du DCA (Dollar Cost Average) (Achats Fixes Réguliers Échelonnés sur Plusieurs Périodes ou Mois).</t>
-  </si>
-  <si>
-    <t>* Décomposer un montant à investir en plusieurs petits montants; tenir compte des frais de transaction.</t>
-  </si>
-  <si>
-    <t>* Rallonger au maximum le temps pendant lequel on sera en mode achat.</t>
-  </si>
-  <si>
-    <t>* Investir en bourse, c'est d'abord comme aller à l'épicerie; on achète.</t>
-  </si>
-  <si>
-    <t>* Investir dans de grandes compagnies qui ont une très forte capitalisation boursière (plusieurs centaines de milliards$).</t>
-  </si>
-  <si>
-    <t>(Exception faite pour des situations où l'action de la compagnie a fait un gain de 20%+ pendant 1 mois).</t>
-  </si>
-  <si>
-    <t>(Exception faite pour des situations de crise généralisée, mondiale).</t>
-  </si>
-  <si>
-    <t>* Contrôler (limiter) les transactions faites lors des périodes de présentation des résultats des compagnies, à cause de la volatilité.</t>
-  </si>
-  <si>
-    <t>(Exception faite pour les transactions régulières programmées (planifiées) à l'avance).</t>
-  </si>
-  <si>
-    <t>* Règles d'investissement; #1:"Protéger le Capital"; #2:"Se rappeler de la règle#1"; #3:"Investir pour le long terme".</t>
-  </si>
-  <si>
-    <t>* Avec un fonds, il n'y a pas de risque de perte permanente du capital (si on ne vend pas lors d'une baisse de la valeur).</t>
-  </si>
-  <si>
-    <t>* Avec une compagnie, il y a un risque de perte permanente du capital (exemple : une compagnie qui fait faillite).</t>
-  </si>
-  <si>
-    <t>* Pertes potentielles (risques) à court terme (en général)</t>
-  </si>
-  <si>
-    <t>* % Investissement (EXEMPLE) par rapport au Total (À ajuster au profil de risque et préférences)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">"Pour atteindre l'autonomie financière, il faut réaliser deux (2) de ces trois (3) facteurs :" 
-"Pour atteindre l'autonomie financière, il faut réaliser deux (2) de ces trois (3) facteurs :" </t>
-  </si>
-  <si>
-    <t xml:space="preserve">1_Avoir de bons revenus; 2_Économiser (épargner); 3_Faire de bons investissements;
-</t>
-  </si>
-  <si>
-    <t>La règle de 72% est utilisée pour calculer le nombre d’années nécessaire à un investissement pour doubler sa valeur, selon le taux d’intérêt (ou le rendement). Il faut diviser le nombre 72 par le taux d’intérêt (ou le rendement) espéré.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">« L'intérêt composé est la huitième merveille du monde. Celui qui le comprend le gagne, et celui qui ne le comprend pas le paie. » </t>
-  </si>
-  <si>
-    <t>* Notation des analystes (Codes de couleur) : Vert (A:Acheter); Jaune (M:Maintenir); Rouge (V:Vendre).</t>
-  </si>
-  <si>
-    <t>* Référence : Yahoo Finance; Yahoo Compare Tool; Average Annual Return; Globe&amp;Mail WatchList, ChatGPT.</t>
-  </si>
-  <si>
-    <t>Gestion des Pertes - Tableau des seuils (ChatGPT)</t>
-  </si>
-  <si>
-    <t>Catégorie
-d'investissement
-(initial)
-(Compagnie)</t>
-  </si>
-  <si>
-    <t>% Investissement (initial) 
-par rapport au Capital (Total)</t>
-  </si>
-  <si>
-    <t>Montant
-Investissement (initial) ($)</t>
-  </si>
-  <si>
-    <t>5 000 $</t>
-  </si>
-  <si>
-    <t>500 $</t>
-  </si>
-  <si>
-    <t>1 000 $</t>
-  </si>
-  <si>
-    <t>2 000 $</t>
-  </si>
-  <si>
-    <t>10 000 $</t>
-  </si>
-  <si>
-    <t>15 000 $</t>
-  </si>
-  <si>
-    <t>1 500 $</t>
-  </si>
-  <si>
-    <t>6,67 %</t>
-  </si>
-  <si>
-    <t>13,33 %</t>
-  </si>
-  <si>
-    <t>20 000 $</t>
-  </si>
-  <si>
-    <t>Exemple : Capital Total = 100 000 $</t>
-  </si>
-  <si>
-    <t>Perte de 10 % sur  investissement
-(initial)
-[Alerte]</t>
-  </si>
-  <si>
-    <t>Exemple pour un Capital-Total de $10 000</t>
-  </si>
-  <si>
-    <t>Calcul Perte de 1 % sur le Capital-Total
-[1 000 $]</t>
-  </si>
-  <si>
-    <t>Calcul Perte de 2 % sur le Capital-Total
-[2 000 $]</t>
-  </si>
-  <si>
-    <t>% Perte sur Investissement-Initial 
-= Égal à 1 % Capital-Total
-[Penser à vendre]</t>
-  </si>
-  <si>
-    <t>% Perte sur 
-Investissement-Initial
-= Égal à 2 % Capital-Total 
-[Vendre]</t>
-  </si>
-  <si>
-    <t>* Les rendements antérieurs ne se répètent pas nécessairement</t>
-  </si>
-  <si>
-    <t>VGG.TO</t>
-  </si>
-  <si>
-    <t>📌 Légende des colonnes clés</t>
-  </si>
-  <si>
-    <t>EXEMPLE pour une répartition "contrôlée" des investissements et des pertes</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">🎯 </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Prix = perte de 10 %</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> : Seuil d'Alerte, à partir duquel on commence à surveiller sérieusement la position.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">🎯 </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Prix = perte de 1 %</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> du Capital-Total (1 000 $) : Seuil d’Alerte Avancée.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">❌ </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Prix = perte de 2 %</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> du Capital-Total (2 000 $) : Seuil de Vente Obligatoire - perte MAXimale sur une position.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Ne pas investir plus de 5 % du Capital-Total</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> dans une (1) seule compagnie; </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>MAX : $ 500 (5 % du Capital-Total)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Ne pas perdre plus de 2 % du Capital-Total</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> dans une (1) seule compagnie; </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>MAX : $200 (2 % du Capital-Total)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">Investir 75 % </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>du Capital-Total dans des fonds [indiciels] (Mondial-1000+; S&amp;P500; NASDAQ-100)</t>
-    </r>
-  </si>
-  <si>
-    <t>* Faire du DCA (Dollar Cost Average) (Achats Fixes Réguliers Échelonnés sur Plusieurs Périodes ou Mois)</t>
-  </si>
-  <si>
-    <t>6) Imprimer en PDF</t>
-  </si>
-  <si>
-    <t>Commande CTRL+ Clic-Gauche, Sélectionner les 3 feuilles (onglets) :</t>
-  </si>
-  <si>
-    <t>"Fonds-Compagnies-Suivi", "Règles d'Investissement", "Contrôle-Pertes-Capital"</t>
-  </si>
-  <si>
-    <t>Commande "File" / "Save As" / Sélectionner le Répertoire / "Save As Type" : PDF</t>
-  </si>
-  <si>
     <t>Croissance Annuelle des Revenus (%)</t>
   </si>
   <si>
@@ -559,25 +216,52 @@
     <t>Total Règle des 40 (Rule of 40) (%)</t>
   </si>
   <si>
+    <t>RSI (Relative Strength Index) / (Court Terme)</t>
+  </si>
+  <si>
     <t>Plage de Valeur (RSI)</t>
   </si>
   <si>
-    <t>2) Installer Python 3.11+ (Windows) et cocher 'Add Python to PATH' (une (1) seule fois)</t>
-  </si>
-  <si>
-    <t>Valeur Min (12 mois, $)</t>
-  </si>
-  <si>
-    <t>Valeur MAX (12 mois, $)</t>
-  </si>
-  <si>
-    <t>RSI (Relative Strength Index) / (Court Terme)</t>
+    <t>50 to 70</t>
+  </si>
+  <si>
+    <t>70 +</t>
+  </si>
+  <si>
+    <t>30 to 50</t>
   </si>
   <si>
     <t>Évaluation de l'Actif (RSI) / (Court Terme)
 (Vert:SurVente; Rouge:SurAchat)</t>
   </si>
   <si>
+    <t>Neutral to Expensive</t>
+  </si>
+  <si>
+    <t>Overvalued</t>
+  </si>
+  <si>
+    <t>Neutral to Undervalued</t>
+  </si>
+  <si>
+    <t>Valeur Min (12 mois, $)</t>
+  </si>
+  <si>
+    <t>Valeur MAX (12 mois, $)</t>
+  </si>
+  <si>
+    <t>Score - indication sur le prix d'achat</t>
+  </si>
+  <si>
+    <t>Ticker</t>
+  </si>
+  <si>
+    <t>Objectif: Mise à jour 1-Clic via Python (YFinance).</t>
+  </si>
+  <si>
+    <t>1) Copier les 4 fichiers dans le même répertoire :</t>
+  </si>
+  <si>
     <t xml:space="preserve">   - MAJ_portefeuille_yahoo_v8_9_yfinance.PY</t>
   </si>
   <si>
@@ -587,19 +271,115 @@
     <t xml:space="preserve">   - MAJ_Portefeuille_Yahoo_v8_9_yfinance.BAT</t>
   </si>
   <si>
+    <t xml:space="preserve">   - Fichier Excel (MODELE.xlsx)</t>
+  </si>
+  <si>
+    <t>2) Installer Python 3.11+ (Windows) et cocher 'Add Python to PATH' (une (1) seule fois)</t>
+  </si>
+  <si>
+    <t>3) Installer les dépendances (une (1) seule fois) :</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   - Ouvrir une Invite de commandes dans ce dossier.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   - Taper :</t>
+  </si>
+  <si>
     <t xml:space="preserve">       py -m pip install -r requirements_yahoo_v8_9_yfinance.txt</t>
   </si>
   <si>
+    <t>4) Mettre à jour :</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   - Fermer Excel (important).</t>
+  </si>
+  <si>
     <t xml:space="preserve">   - Glisser - Déposer le fichier "MODELE.xlsx" sur "MAJ_Portefeuille_Yahoo_v8_9_yfinance.bat"</t>
   </si>
   <si>
-    <t>Score - indication sur le prix d'achat</t>
+    <t xml:space="preserve">   - Un fichier *_MAJ.xlsx est créé + un *_LOG.txt.</t>
+  </si>
+  <si>
+    <t>5) Personnaliser (si besoin) :</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   - Modifie les tickers sur la ligne 3 (B→...). Le script suivra automatiquement.</t>
+  </si>
+  <si>
+    <t>6) Imprimer en PDF</t>
+  </si>
+  <si>
+    <t>Commande CTRL+ Clic-Gauche, Sélectionner les 3 feuilles (onglets) :</t>
+  </si>
+  <si>
+    <t>"Fonds-Compagnies-Suivi", "Règles d'Investissement", "Contrôle-Pertes-Capital"</t>
+  </si>
+  <si>
+    <t>Commande "File" / "Save As" / Sélectionner le Répertoire / "Save As Type" : PDF</t>
+  </si>
+  <si>
+    <t>* Règles d'Investissement</t>
+  </si>
+  <si>
+    <t>* "Les rendements antérieurs ne se répètent pas nécessairement".</t>
+  </si>
+  <si>
+    <t>* Regarder principalement le rendement sur 10 ans (les fonds indiciels en priorité).</t>
+  </si>
+  <si>
+    <t>* Prendre avec prudence les rendements trop élevés (&gt;30%, pas de garantie).</t>
+  </si>
+  <si>
+    <t>* S'assurer qu'on peut tolérer le niveau de risque associé à un fonds ou à l'action d'une compagnie.</t>
+  </si>
+  <si>
+    <t>* Faire du DCA (Dollar Cost Average) (Achats Fixes Réguliers Échelonnés sur Plusieurs Périodes ou Mois).</t>
+  </si>
+  <si>
+    <t>* Décomposer un montant à investir en plusieurs petits montants; tenir compte des frais de transaction.</t>
+  </si>
+  <si>
+    <t>* Rallonger au maximum le temps pendant lequel on sera en mode achat.</t>
+  </si>
+  <si>
+    <t>* Investir en bourse, c'est d'abord comme aller à l'épicerie; on achète.</t>
+  </si>
+  <si>
+    <t>* Investir dans de grandes compagnies qui ont une très forte capitalisation boursière (plusieurs centaines de milliards$).</t>
+  </si>
+  <si>
+    <t>* Investir un MAXimum de 5% de votre portefeuille (capital) dans l'action d'une seule compagnie, généralement.</t>
   </si>
   <si>
     <t>* Prendre une partie des bénéfices quand l'action d'une compagnie augmente de 20% à 25% par rapport au prix d'achat.</t>
   </si>
   <si>
+    <t>(Exception faite pour des situations où l'action de la compagnie a fait un gain de 20%+ pendant 1 mois).</t>
+  </si>
+  <si>
     <t>* Penser à vendre l'action d'une compagnie si elle perd 10% du prix d'achat (ou 1% (2% MAX) du portefeuille), pour limiter les pertes.</t>
+  </si>
+  <si>
+    <t>(Exception faite pour des situations de crise généralisée, mondiale).</t>
+  </si>
+  <si>
+    <t>* Contrôler (limiter) les transactions faites lors des périodes de présentation des résultats des compagnies, à cause de la volatilité.</t>
+  </si>
+  <si>
+    <t>(Exception faite pour les transactions régulières programmées (planifiées) à l'avance).</t>
+  </si>
+  <si>
+    <t>* Règles d'investissement; #1:"Protéger le Capital"; #2:"Se rappeler de la règle#1"; #3:"Investir pour le long terme".</t>
+  </si>
+  <si>
+    <t>* Avec un fonds, il n'y a pas de risque de perte permanente du capital (si on ne vend pas lors d'une baisse de la valeur).</t>
+  </si>
+  <si>
+    <t>* Avec une compagnie, il y a un risque de perte permanente du capital (exemple : une compagnie qui fait faillite).</t>
+  </si>
+  <si>
+    <t>* Pertes potentielles (risques) à court terme (en général)</t>
   </si>
   <si>
     <t>(-10% pour Fonds MONDIAL); 
@@ -610,6 +390,9 @@
 (-30% (et plus) pour Actions Compagnies);</t>
   </si>
   <si>
+    <t>* % Investissement (EXEMPLE) par rapport au Total (À ajuster au profil de risque et préférences)</t>
+  </si>
+  <si>
     <t>(50%+ pour Fonds MONDIAL); 
 (0% à 25% pour Fonds USA-TOTAL);
 (0% à 25% pour Fonds S&amp;P-500);
@@ -618,147 +401,148 @@
 (0% à 25% pour le TOTAL d'actions de compagnies; MAXimum de 5% pour l'action d'une seule compagnie);</t>
   </si>
   <si>
+    <t xml:space="preserve">"Pour atteindre l'autonomie financière, il faut réaliser deux (2) de ces trois (3) facteurs :" 
+"Pour atteindre l'autonomie financière, il faut réaliser deux (2) de ces trois (3) facteurs :" </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1_Avoir de bons revenus; 2_Économiser (épargner); 3_Faire de bons investissements;
+</t>
+  </si>
+  <si>
     <t>« Règle du 72% » : Doubler la valeur du capital (72 = Rendement annuel moyen * Nombre d'années)</t>
   </si>
   <si>
-    <t>* Investir un MAXimum de 5% de votre portefeuille (capital) dans l'action d'une seule compagnie, généralement.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DIVIDENDE
-(VIC200, VGG, RBF902)
-(VDY, RBF646, FID2930)
- [VYM, VIG, SCHD] 
-</t>
-  </si>
-  <si>
-    <t>VUN.TO</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">OR </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">
-(Indice métal)
-(CGL.TO, PHYS.TO)
-[IAU]</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>CHIPS</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">
-(XCHP.TO, CHPS.TO)
-[SOXX, SMH]</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Investir un MAX de 25 %</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> du Capital-Total dans environ cinq (5) compagnies (</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>5 % MAX</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> dans une (1) compagnie)</t>
-    </r>
-  </si>
-  <si>
-    <t>CGL.TO</t>
-  </si>
-  <si>
-    <t>XCHP.TO</t>
-  </si>
-  <si>
-    <t>NVDA.TO</t>
-  </si>
-  <si>
-    <t>AVGO.TO</t>
-  </si>
-  <si>
-    <t>AAPL.TO</t>
-  </si>
-  <si>
-    <t>GOOG.TO</t>
-  </si>
-  <si>
-    <t>ORAC.TO</t>
-  </si>
-  <si>
-    <t>Vernova
-(gev.cdr)</t>
-  </si>
-  <si>
-    <t>GEV.TO</t>
+    <t>La règle de 72% est utilisée pour calculer le nombre d’années nécessaire à un investissement pour doubler sa valeur, selon le taux d’intérêt (ou le rendement). Il faut diviser le nombre 72 par le taux d’intérêt (ou le rendement) espéré.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">« L'intérêt composé est la huitième merveille du monde. Celui qui le comprend le gagne, et celui qui ne le comprend pas le paie. » </t>
+  </si>
+  <si>
+    <t>* Notation des analystes (Codes de couleur) : Vert (A:Acheter); Jaune (M:Maintenir); Rouge (V:Vendre).</t>
+  </si>
+  <si>
+    <t>* Référence : Yahoo Finance; Yahoo Compare Tool; Average Annual Return; Globe&amp;Mail WatchList, ChatGPT.</t>
+  </si>
+  <si>
+    <t>Gestion des Pertes - Tableau des seuils (ChatGPT)</t>
+  </si>
+  <si>
+    <t>Exemple : Capital Total = 100 000 $</t>
+  </si>
+  <si>
+    <t>Catégorie
+d'investissement
+(initial)
+(Compagnie)</t>
+  </si>
+  <si>
+    <t>% Investissement (initial) 
+par rapport au Capital (Total)</t>
+  </si>
+  <si>
+    <t>Montant
+Investissement (initial) ($)</t>
+  </si>
+  <si>
+    <t>Perte de 10 % sur  investissement
+(initial)
+[Alerte]</t>
+  </si>
+  <si>
+    <t>Calcul Perte de 1 % sur le Capital-Total
+[1 000 $]</t>
+  </si>
+  <si>
+    <t>% Perte sur Investissement-Initial 
+= Égal à 1 % Capital-Total
+[Penser à vendre]</t>
+  </si>
+  <si>
+    <t>Calcul Perte de 2 % sur le Capital-Total
+[2 000 $]</t>
+  </si>
+  <si>
+    <t>% Perte sur 
+Investissement-Initial
+= Égal à 2 % Capital-Total 
+[Vendre]</t>
+  </si>
+  <si>
+    <t>5 000 $</t>
+  </si>
+  <si>
+    <t>500 $</t>
+  </si>
+  <si>
+    <t>1 000 $</t>
+  </si>
+  <si>
+    <t>2 000 $</t>
+  </si>
+  <si>
+    <t>10 000 $</t>
+  </si>
+  <si>
+    <t>15 000 $</t>
+  </si>
+  <si>
+    <t>1 500 $</t>
+  </si>
+  <si>
+    <t>6,67 %</t>
+  </si>
+  <si>
+    <t>13,33 %</t>
+  </si>
+  <si>
+    <t>20 000 $</t>
+  </si>
+  <si>
+    <t>📌 Légende des colonnes clés</t>
+  </si>
+  <si>
+    <t>🎯 Prix = perte de 10 % : Seuil d'Alerte, à partir duquel on commence à surveiller sérieusement la position.</t>
+  </si>
+  <si>
+    <t>🎯 Prix = perte de 1 % du Capital-Total (1 000 $) : Seuil d’Alerte Avancée.</t>
+  </si>
+  <si>
+    <t>❌ Prix = perte de 2 % du Capital-Total (2 000 $) : Seuil de Vente Obligatoire - perte MAXimale sur une position.</t>
+  </si>
+  <si>
+    <t>Exemple pour un Capital-Total de $10 000</t>
+  </si>
+  <si>
+    <t>Ne pas investir plus de 5 % du Capital-Total dans une (1) seule compagnie; MAX : $ 500 (5 % du Capital-Total)</t>
+  </si>
+  <si>
+    <t>Ne pas perdre plus de 2 % du Capital-Total dans une (1) seule compagnie; MAX : $200 (2 % du Capital-Total)</t>
+  </si>
+  <si>
+    <t>EXEMPLE pour une répartition "contrôlée" des investissements et des pertes</t>
+  </si>
+  <si>
+    <t>Investir 75 % du Capital-Total dans des fonds [indiciels] (Mondial-1000+; S&amp;P500; NASDAQ-100)</t>
+  </si>
+  <si>
+    <t>Investir un MAX de 25 % du Capital-Total dans environ cinq (5) compagnies (5 % MAX dans une (1) compagnie)</t>
+  </si>
+  <si>
+    <t>* Faire du DCA (Dollar Cost Average) (Achats Fixes Réguliers Échelonnés sur Plusieurs Périodes ou Mois)</t>
+  </si>
+  <si>
+    <t>* Les rendements antérieurs ne se répètent pas nécessairement</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0"/>
+    <numFmt numFmtId="166" formatCode="yyyy\-mm\-dd;@"/>
   </numFmts>
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="17" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -881,14 +665,8 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b/>
-      <sz val="12"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
   </fonts>
-  <fills count="9">
+  <fills count="14">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -937,6 +715,36 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCE4D6"/>
+        <bgColor rgb="FFFCE4D6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4CCCC"/>
+        <bgColor rgb="FFF4CCCC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4B183"/>
+        <bgColor rgb="FFF4B183"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor rgb="FFC6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFD966"/>
+        <bgColor rgb="FFFFD966"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="114">
     <border>
@@ -2445,7 +2253,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="382">
+  <cellXfs count="385">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -2471,9 +2279,6 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
     <xf numFmtId="9" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
@@ -2678,9 +2483,6 @@
     <xf numFmtId="9" fontId="8" fillId="0" borderId="51" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -2785,8 +2587,7 @@
     <xf numFmtId="9" fontId="8" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2822,7 +2623,7 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -2861,16 +2662,16 @@
     <xf numFmtId="1" fontId="8" fillId="2" borderId="64" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2892,18 +2693,6 @@
     <xf numFmtId="0" fontId="7" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="2" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="2" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="2" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="2" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
@@ -2922,7 +2711,7 @@
     <xf numFmtId="9" fontId="11" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="164" fontId="8" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2979,18 +2768,6 @@
     <xf numFmtId="0" fontId="10" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="7" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -3036,16 +2813,10 @@
     <xf numFmtId="1" fontId="8" fillId="0" borderId="76" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="76" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="74" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="76" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="8" fillId="0" borderId="77" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="2" borderId="80" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="2" borderId="82" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3087,16 +2858,10 @@
     <xf numFmtId="1" fontId="8" fillId="0" borderId="85" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="85" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="83" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="85" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="8" fillId="0" borderId="86" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="2" borderId="89" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3138,34 +2903,22 @@
     <xf numFmtId="1" fontId="8" fillId="0" borderId="49" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="90" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="8" fillId="0" borderId="93" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="2" borderId="51" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="1" fontId="8" fillId="2" borderId="65" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="1" fontId="8" fillId="0" borderId="56" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="8" fillId="0" borderId="65" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="2" borderId="95" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="97" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3207,16 +2960,10 @@
     <xf numFmtId="1" fontId="8" fillId="0" borderId="100" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="100" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="98" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="100" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="8" fillId="0" borderId="101" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="2" borderId="104" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="8" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3309,33 +3056,6 @@
     <xf numFmtId="0" fontId="11" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="1" fontId="11" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="11" fillId="3" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="11" fillId="3" borderId="54" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="11" fillId="3" borderId="96" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="11" fillId="3" borderId="91" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="11" fillId="3" borderId="72" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="11" fillId="3" borderId="81" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="11" fillId="3" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="11" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="3" borderId="66" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
@@ -3480,19 +3200,10 @@
     <xf numFmtId="1" fontId="7" fillId="2" borderId="110" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="109" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="107" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="109" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="8" fillId="0" borderId="110" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="2" borderId="113" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="11" fillId="3" borderId="105" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3563,6 +3274,114 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="82" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="107" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="98" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="12" borderId="90" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="83" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="74" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="83" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="12" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="10" borderId="113" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="10" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="10" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="10" borderId="95" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="10" borderId="104" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="51" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="10" borderId="89" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="10" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="10" borderId="80" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="9" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="9" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="11" fillId="11" borderId="105" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="11" fillId="11" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="11" fillId="11" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="11" fillId="11" borderId="54" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="11" fillId="11" borderId="96" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="11" fillId="13" borderId="91" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="11" fillId="11" borderId="81" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="11" fillId="13" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="11" fillId="13" borderId="72" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="11" fillId="13" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="11" fillId="13" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="7" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -4202,11 +4021,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="23.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="38" t="s">
+      <c r="A1" s="37" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="38" t="s">
-        <v>1</v>
+      <c r="B1" s="384">
+        <v>46143</v>
       </c>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
@@ -4220,887 +4039,1005 @@
       <c r="N1" s="1"/>
     </row>
     <row r="2" spans="1:14" ht="60" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="39" t="s">
+      <c r="A2" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="305" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="335" t="s">
+      <c r="C2" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="D2" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="E2" s="120" t="s">
         <v>5</v>
       </c>
-      <c r="E2" s="123" t="s">
+      <c r="F2" s="231" t="s">
         <v>6</v>
       </c>
-      <c r="F2" s="250" t="s">
-        <v>131</v>
-      </c>
-      <c r="G2" s="227" t="s">
-        <v>133</v>
-      </c>
-      <c r="H2" s="381" t="s">
-        <v>134</v>
-      </c>
-      <c r="I2" s="184" t="s">
+      <c r="G2" s="212" t="s">
         <v>7</v>
       </c>
-      <c r="J2" s="193" t="s">
+      <c r="H2" s="348" t="s">
+        <v>8</v>
+      </c>
+      <c r="I2" s="177" t="s">
+        <v>9</v>
+      </c>
+      <c r="J2" s="182" t="s">
         <v>10</v>
       </c>
-      <c r="K2" s="210" t="s">
-        <v>9</v>
-      </c>
-      <c r="L2" s="184" t="s">
-        <v>8</v>
-      </c>
-      <c r="M2" s="185" t="s">
+      <c r="K2" s="197" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="186" t="s">
-        <v>143</v>
+      <c r="L2" s="177" t="s">
+        <v>12</v>
+      </c>
+      <c r="M2" s="178" t="s">
+        <v>13</v>
+      </c>
+      <c r="N2" s="179" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:14" ht="33.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="B3" s="336" t="s">
-        <v>13</v>
-      </c>
-      <c r="C3" s="34" t="s">
-        <v>132</v>
-      </c>
-      <c r="D3" s="35" t="s">
-        <v>14</v>
-      </c>
-      <c r="E3" s="124" t="s">
         <v>15</v>
       </c>
-      <c r="F3" s="251" t="s">
-        <v>96</v>
-      </c>
-      <c r="G3" s="228" t="s">
-        <v>136</v>
-      </c>
-      <c r="H3" s="211" t="s">
-        <v>137</v>
-      </c>
-      <c r="I3" s="36" t="s">
-        <v>138</v>
-      </c>
-      <c r="J3" s="194" t="s">
-        <v>139</v>
-      </c>
-      <c r="K3" s="211" t="s">
-        <v>140</v>
-      </c>
-      <c r="L3" s="36" t="s">
-        <v>141</v>
-      </c>
-      <c r="M3" s="34" t="s">
-        <v>142</v>
-      </c>
-      <c r="N3" s="37" t="s">
-        <v>144</v>
+      <c r="B3" s="306" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" s="33" t="s">
+        <v>17</v>
+      </c>
+      <c r="D3" s="34" t="s">
+        <v>18</v>
+      </c>
+      <c r="E3" s="121" t="s">
+        <v>19</v>
+      </c>
+      <c r="F3" s="232" t="s">
+        <v>20</v>
+      </c>
+      <c r="G3" s="213" t="s">
+        <v>21</v>
+      </c>
+      <c r="H3" s="198" t="s">
+        <v>22</v>
+      </c>
+      <c r="I3" s="35" t="s">
+        <v>23</v>
+      </c>
+      <c r="J3" s="183" t="s">
+        <v>24</v>
+      </c>
+      <c r="K3" s="198" t="s">
+        <v>25</v>
+      </c>
+      <c r="L3" s="35" t="s">
+        <v>26</v>
+      </c>
+      <c r="M3" s="33" t="s">
+        <v>27</v>
+      </c>
+      <c r="N3" s="36" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="33" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A4" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="B4" s="337">
-        <v>111.40000152587891</v>
-      </c>
-      <c r="C4" s="174">
-        <v>46.680000305175781</v>
-      </c>
-      <c r="D4" s="175">
-        <v>70.860000610351563</v>
-      </c>
-      <c r="E4" s="176">
-        <v>63.849998474121087</v>
-      </c>
-      <c r="F4" s="252">
-        <v>83.199996948242188</v>
-      </c>
-      <c r="G4" s="229">
-        <v>39.830001831054688</v>
-      </c>
-      <c r="H4" s="212">
-        <v>188.52000427246091</v>
-      </c>
-      <c r="I4" s="177">
-        <v>335</v>
-      </c>
-      <c r="J4" s="195">
-        <v>480.57998657226563</v>
-      </c>
-      <c r="K4" s="212">
-        <v>258.26998901367188</v>
-      </c>
-      <c r="L4" s="177">
-        <v>332.79000854492188</v>
-      </c>
-      <c r="M4" s="174">
-        <v>174.8999938964844</v>
-      </c>
-      <c r="N4" s="178">
-        <v>165.69999694824219</v>
+        <v>29</v>
+      </c>
+      <c r="B4" s="307">
+        <v>117.9300003051758</v>
+      </c>
+      <c r="C4" s="167">
+        <v>135.5299987792969</v>
+      </c>
+      <c r="D4" s="168">
+        <v>74.830001831054688</v>
+      </c>
+      <c r="E4" s="169">
+        <v>71.080001831054688</v>
+      </c>
+      <c r="F4" s="233">
+        <v>107.4199981689453</v>
+      </c>
+      <c r="G4" s="214">
+        <v>34.779998779296882</v>
+      </c>
+      <c r="H4" s="199">
+        <v>121.61000061035161</v>
+      </c>
+      <c r="I4" s="170">
+        <v>50.810001373291023</v>
+      </c>
+      <c r="J4" s="184">
+        <v>16.260000228881839</v>
+      </c>
+      <c r="K4" s="199">
+        <v>42.520000457763672</v>
+      </c>
+      <c r="L4" s="170">
+        <v>62.959999084472663</v>
+      </c>
+      <c r="M4" s="167">
+        <v>9.619999885559082</v>
+      </c>
+      <c r="N4" s="171">
+        <v>70.900001525878906</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="29.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="B5" s="338"/>
-      <c r="C5" s="169"/>
-      <c r="D5" s="170"/>
-      <c r="E5" s="171"/>
-      <c r="F5" s="253"/>
-      <c r="G5" s="230"/>
-      <c r="H5" s="213">
-        <v>4589.8965975040001</v>
-      </c>
-      <c r="I5" s="172">
-        <v>4044.064292864</v>
-      </c>
-      <c r="J5" s="196">
-        <v>3572.2310451200001</v>
-      </c>
-      <c r="K5" s="213">
-        <v>3816.2884198400002</v>
-      </c>
-      <c r="L5" s="172">
-        <v>1577.8485370880001</v>
-      </c>
-      <c r="M5" s="169">
-        <v>502.51041996800001</v>
-      </c>
-      <c r="N5" s="173">
-        <v>394.93536972800001</v>
+        <v>30</v>
+      </c>
+      <c r="B5" s="308"/>
+      <c r="C5" s="162"/>
+      <c r="D5" s="163"/>
+      <c r="E5" s="164"/>
+      <c r="F5" s="234"/>
+      <c r="G5" s="215"/>
+      <c r="H5" s="200"/>
+      <c r="I5" s="165">
+        <v>7111.2044052479996</v>
+      </c>
+      <c r="J5" s="185">
+        <v>436.07585587199998</v>
+      </c>
+      <c r="K5" s="200">
+        <v>5823.8597857280001</v>
+      </c>
+      <c r="L5" s="165">
+        <v>6263.1612252160003</v>
+      </c>
+      <c r="M5" s="162">
+        <v>752.56332287999999</v>
+      </c>
+      <c r="N5" s="166">
+        <v>380.796665856</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="30.6" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="296" t="s">
-        <v>18</v>
-      </c>
-      <c r="B6" s="339">
-        <v>0.1248175032758856</v>
-      </c>
-      <c r="C6" s="316"/>
-      <c r="D6" s="317">
-        <v>0.13597614223066601</v>
-      </c>
-      <c r="E6" s="318">
-        <v>0.18288494661017429</v>
-      </c>
-      <c r="F6" s="319"/>
-      <c r="G6" s="320">
-        <v>0.15001190705111611</v>
-      </c>
-      <c r="H6" s="322">
-        <v>0.74677716224364254</v>
-      </c>
-      <c r="I6" s="323">
-        <v>0.247025703780789</v>
-      </c>
-      <c r="J6" s="321">
-        <v>0.25857533877080341</v>
-      </c>
-      <c r="K6" s="322">
-        <v>0.2797159395319877</v>
-      </c>
-      <c r="L6" s="323">
-        <v>0.41686234047228687</v>
-      </c>
-      <c r="M6" s="316">
-        <v>0.18798204558813031</v>
-      </c>
-      <c r="N6" s="324"/>
+      <c r="A6" s="275" t="s">
+        <v>31</v>
+      </c>
+      <c r="B6" s="309">
+        <v>0.13410207649526831</v>
+      </c>
+      <c r="C6" s="286">
+        <v>0.15440002429360281</v>
+      </c>
+      <c r="D6" s="287">
+        <v>0.13560434235056329</v>
+      </c>
+      <c r="E6" s="288">
+        <v>0.1942199192288814</v>
+      </c>
+      <c r="F6" s="289">
+        <v>0.13219596325083491</v>
+      </c>
+      <c r="G6" s="290">
+        <v>0.1188753448338784</v>
+      </c>
+      <c r="H6" s="292"/>
+      <c r="I6" s="293"/>
+      <c r="J6" s="291"/>
+      <c r="K6" s="292"/>
+      <c r="L6" s="293"/>
+      <c r="M6" s="286"/>
+      <c r="N6" s="294"/>
     </row>
     <row r="7" spans="1:14" ht="28.8" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="162" t="s">
-        <v>19</v>
-      </c>
-      <c r="B7" s="340">
-        <v>-1.4333703462261481E-2</v>
-      </c>
-      <c r="C7" s="163">
-        <v>-3.0523705258934771E-2</v>
-      </c>
-      <c r="D7" s="164">
-        <v>-7.0516216577964919E-4</v>
-      </c>
-      <c r="E7" s="165">
-        <v>-3.2706493737055593E-2</v>
-      </c>
-      <c r="F7" s="254">
-        <v>-5.8550063193884014E-3</v>
-      </c>
-      <c r="G7" s="231">
+      <c r="A7" s="155" t="s">
+        <v>32</v>
+      </c>
+      <c r="B7" s="310">
+        <v>-1.1069179830811021E-2</v>
+      </c>
+      <c r="C7" s="156">
+        <v>-1.029650676917937E-2</v>
+      </c>
+      <c r="D7" s="157">
+        <v>-1.2275610862622081E-2</v>
+      </c>
+      <c r="E7" s="158">
+        <v>-1.55123984006591E-2</v>
+      </c>
+      <c r="F7" s="235">
+        <v>-4.0793847479732026E-3</v>
+      </c>
+      <c r="G7" s="216">
+        <v>-0.16132149130650111</v>
+      </c>
+      <c r="H7" s="201">
+        <v>-3.9187794077836902E-2</v>
+      </c>
+      <c r="I7" s="159">
+        <v>-4.1863048408602888E-2</v>
+      </c>
+      <c r="J7" s="186">
+        <v>-3.3293666831320068E-2</v>
+      </c>
+      <c r="K7" s="201">
         <v>0</v>
       </c>
-      <c r="H7" s="214">
-        <v>-8.9400594848781156E-2</v>
-      </c>
-      <c r="I7" s="166">
-        <v>-4.2504910588020417E-3</v>
-      </c>
-      <c r="J7" s="197">
-        <v>-0.1117762911796969</v>
-      </c>
-      <c r="K7" s="214">
-        <v>-9.755761273823893E-2</v>
-      </c>
-      <c r="L7" s="166">
-        <v>-0.19261261992315029</v>
-      </c>
-      <c r="M7" s="163">
-        <v>-0.46496921188416879</v>
-      </c>
-      <c r="N7" s="167">
-        <v>-0.20021236216786459</v>
+      <c r="L7" s="159">
+        <v>-1.625001430511475E-2</v>
+      </c>
+      <c r="M7" s="156">
+        <v>-6.0928006690886161E-2</v>
+      </c>
+      <c r="N7" s="160">
+        <v>-9.4855101895709226E-2</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="31.8" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="359" t="s">
-        <v>20</v>
-      </c>
-      <c r="B8" s="360">
-        <v>1.291570766989758E-2</v>
-      </c>
-      <c r="C8" s="361">
-        <v>2.2624632666077278E-3</v>
-      </c>
-      <c r="D8" s="362">
-        <v>5.6535898032255014E-3</v>
-      </c>
-      <c r="E8" s="363">
-        <v>-1.3165230368243019E-2</v>
-      </c>
-      <c r="F8" s="364"/>
-      <c r="G8" s="365">
-        <v>0.15549754628764781</v>
-      </c>
-      <c r="H8" s="367">
-        <v>-1.054949099729041E-2</v>
-      </c>
-      <c r="I8" s="368">
-        <v>6.3627156110652061E-2</v>
-      </c>
-      <c r="J8" s="366">
-        <v>-1.4619353730154661E-2</v>
-      </c>
-      <c r="K8" s="367">
-        <v>-5.5340180031390518E-2</v>
-      </c>
-      <c r="L8" s="368">
-        <v>-5.4922886631961099E-2</v>
-      </c>
-      <c r="M8" s="361">
-        <v>-0.1142869815498703</v>
-      </c>
-      <c r="N8" s="369">
-        <v>-0.1219331723119171</v>
+      <c r="A8" s="326" t="s">
+        <v>33</v>
+      </c>
+      <c r="B8" s="327">
+        <v>3.683842553280825E-2</v>
+      </c>
+      <c r="C8" s="328">
+        <v>5.1680017959596647E-2</v>
+      </c>
+      <c r="D8" s="329">
+        <v>5.3498565635135657E-2</v>
+      </c>
+      <c r="E8" s="330">
+        <v>0.1088924106566338</v>
+      </c>
+      <c r="F8" s="331">
+        <v>2.3925216082539169E-2</v>
+      </c>
+      <c r="G8" s="332">
+        <v>-5.1799386861259178E-2</v>
+      </c>
+      <c r="H8" s="334">
+        <v>0.26968054040775291</v>
+      </c>
+      <c r="I8" s="335">
+        <v>0.13491179034553549</v>
+      </c>
+      <c r="J8" s="333">
+        <v>6.8331139527374907E-2</v>
+      </c>
+      <c r="K8" s="334">
+        <v>0.12440887485401859</v>
+      </c>
+      <c r="L8" s="335">
+        <v>0.17156674949826509</v>
+      </c>
+      <c r="M8" s="328">
+        <v>0.13577326827330569</v>
+      </c>
+      <c r="N8" s="336">
+        <v>5.7735384410857682E-2</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="B9" s="341">
-        <v>6.7388400587629071E-3</v>
-      </c>
-      <c r="C9" s="12">
-        <v>-9.6085969748782585E-3</v>
-      </c>
-      <c r="D9" s="13">
-        <v>1.0205314699309961E-2</v>
-      </c>
-      <c r="E9" s="125">
-        <v>-2.8800106207165999E-2</v>
-      </c>
-      <c r="F9" s="255"/>
-      <c r="G9" s="232">
-        <v>0.30163403053989257</v>
-      </c>
-      <c r="H9" s="215">
-        <v>-6.2177313458077872E-2</v>
-      </c>
-      <c r="I9" s="14">
-        <v>0.24881188426310771</v>
-      </c>
-      <c r="J9" s="198">
-        <v>-0.1117762911796969</v>
-      </c>
-      <c r="K9" s="215">
-        <v>-3.8957739873303088E-2</v>
-      </c>
-      <c r="L9" s="14">
-        <v>-0.1060225488457627</v>
-      </c>
-      <c r="M9" s="12">
-        <v>-0.3755569855488835</v>
-      </c>
-      <c r="N9" s="15">
-        <v>-0.12605489655008131</v>
+      <c r="A9" s="161" t="s">
+        <v>34</v>
+      </c>
+      <c r="B9" s="311">
+        <v>6.57930291812443E-2</v>
+      </c>
+      <c r="C9" s="11">
+        <v>9.0827365132665427E-2</v>
+      </c>
+      <c r="D9" s="12">
+        <v>7.8397499484886612E-2</v>
+      </c>
+      <c r="E9" s="122">
+        <v>0.16850237862013701</v>
+      </c>
+      <c r="F9" s="236">
+        <v>2.2785115775777239E-2</v>
+      </c>
+      <c r="G9" s="217">
+        <v>-0.1012920389241055</v>
+      </c>
+      <c r="H9" s="202">
+        <v>0.44911824670836897</v>
+      </c>
+      <c r="I9" s="13">
+        <v>0.22735348142807729</v>
+      </c>
+      <c r="J9" s="187">
+        <v>0.29729094291000879</v>
+      </c>
+      <c r="K9" s="202">
+        <v>0.16759600273233291</v>
+      </c>
+      <c r="L9" s="13">
+        <v>0.27179176027792251</v>
+      </c>
+      <c r="M9" s="11">
+        <v>0.20821779179664121</v>
+      </c>
+      <c r="N9" s="14">
+        <v>0.30266007164696629</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="B10" s="342">
-        <v>0.1012501744104926</v>
-      </c>
-      <c r="C10" s="17">
-        <v>8.1354196886832764E-2</v>
-      </c>
-      <c r="D10" s="18">
-        <v>9.0904456731398353E-2</v>
-      </c>
-      <c r="E10" s="126">
-        <v>8.0640377416913545E-2</v>
-      </c>
-      <c r="F10" s="256"/>
-      <c r="G10" s="233">
-        <v>0.53783793118506962</v>
-      </c>
-      <c r="H10" s="216">
-        <v>7.4247274177905886E-2</v>
-      </c>
-      <c r="I10" s="19">
-        <v>0.70808024115728863</v>
-      </c>
-      <c r="J10" s="199">
-        <v>-5.9112016649575772E-2</v>
-      </c>
-      <c r="K10" s="216">
-        <v>0.2250378726441282</v>
-      </c>
-      <c r="L10" s="19">
-        <v>0.1229843439289602</v>
-      </c>
-      <c r="M10" s="17">
-        <v>-0.29727718840396139</v>
-      </c>
-      <c r="N10" s="20">
-        <v>6.0547818244233387E-2</v>
-      </c>
+      <c r="A10" s="15" t="s">
+        <v>35</v>
+      </c>
+      <c r="B10" s="312">
+        <v>7.7931421637679854E-2</v>
+      </c>
+      <c r="C10" s="16">
+        <v>8.3948824537549482E-2</v>
+      </c>
+      <c r="D10" s="17">
+        <v>9.2453319011020829E-2</v>
+      </c>
+      <c r="E10" s="123">
+        <v>0.12539877460685431</v>
+      </c>
+      <c r="F10" s="237">
+        <v>4.2519547212818143E-2</v>
+      </c>
+      <c r="G10" s="218">
+        <v>0.1013299196745308</v>
+      </c>
+      <c r="H10" s="203">
+        <v>0.7249645476645612</v>
+      </c>
+      <c r="I10" s="18">
+        <v>0.17328383876581749</v>
+      </c>
+      <c r="J10" s="188"/>
+      <c r="K10" s="203">
+        <v>9.255264268859964E-2</v>
+      </c>
+      <c r="L10" s="18">
+        <v>0.40039045613146712</v>
+      </c>
+      <c r="M10" s="16"/>
+      <c r="N10" s="19"/>
     </row>
     <row r="11" spans="1:14" ht="33.6" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="370" t="s">
-        <v>23</v>
-      </c>
-      <c r="B11" s="371">
-        <v>1.9586301920259789E-2</v>
-      </c>
-      <c r="C11" s="372">
-        <v>1.1484263527048229E-2</v>
-      </c>
-      <c r="D11" s="373">
-        <v>1.7957189901448119E-2</v>
-      </c>
-      <c r="E11" s="374">
-        <v>2.5044108776130839E-2</v>
-      </c>
-      <c r="F11" s="375">
-        <v>2.564095329431915E-2</v>
-      </c>
-      <c r="G11" s="376">
-        <v>0.1996988227637688</v>
-      </c>
-      <c r="H11" s="378">
-        <v>1.083112210434822E-2</v>
-      </c>
-      <c r="I11" s="379">
-        <v>6.7558996277010896E-2</v>
-      </c>
-      <c r="J11" s="377">
-        <v>-6.2859446995884296E-3</v>
-      </c>
-      <c r="K11" s="378">
-        <v>-4.9988954131356962E-2</v>
-      </c>
-      <c r="L11" s="379">
-        <v>-3.8457085593384337E-2</v>
-      </c>
-      <c r="M11" s="372">
-        <v>-0.1002907783353852</v>
-      </c>
-      <c r="N11" s="380">
-        <v>-6.7791859644207086E-2</v>
+      <c r="A11" s="337" t="s">
+        <v>36</v>
+      </c>
+      <c r="B11" s="338">
+        <v>7.9351986083023851E-2</v>
+      </c>
+      <c r="C11" s="339">
+        <v>8.6117626688129612E-2</v>
+      </c>
+      <c r="D11" s="340">
+        <v>7.4989242564765357E-2</v>
+      </c>
+      <c r="E11" s="341">
+        <v>0.1411141561459861</v>
+      </c>
+      <c r="F11" s="342">
+        <v>4.7245973889946447E-2</v>
+      </c>
+      <c r="G11" s="343">
+        <v>4.7590300603882703E-2</v>
+      </c>
+      <c r="H11" s="345">
+        <v>0.69326094579634923</v>
+      </c>
+      <c r="I11" s="346">
+        <v>0.20067198502316949</v>
+      </c>
+      <c r="J11" s="344">
+        <v>0.21596825359920929</v>
+      </c>
+      <c r="K11" s="345">
+        <v>9.6489831878346033E-2</v>
+      </c>
+      <c r="L11" s="346">
+        <v>0.24073585713581219</v>
+      </c>
+      <c r="M11" s="339">
+        <v>-1.392651601219419E-2</v>
+      </c>
+      <c r="N11" s="347">
+        <v>0.59467837938687551</v>
       </c>
     </row>
     <row r="12" spans="1:14" ht="32.4" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="277" t="s">
-        <v>24</v>
-      </c>
-      <c r="B12" s="343">
-        <v>0.1449678994555641</v>
-      </c>
-      <c r="C12" s="278"/>
-      <c r="D12" s="279">
-        <v>0.1516413653927893</v>
-      </c>
-      <c r="E12" s="280">
-        <v>0.1829913217066779</v>
-      </c>
-      <c r="F12" s="281"/>
-      <c r="G12" s="282">
-        <v>0.83964098707315471</v>
-      </c>
-      <c r="H12" s="284">
-        <v>0.59290379116464509</v>
-      </c>
-      <c r="I12" s="285">
-        <v>0.73623983965093553</v>
-      </c>
-      <c r="J12" s="283">
-        <v>0.1141406262538802</v>
-      </c>
-      <c r="K12" s="284">
-        <v>0.12877221890942089</v>
-      </c>
-      <c r="L12" s="285">
-        <v>0.66187086034333631</v>
-      </c>
-      <c r="M12" s="278">
-        <v>0.1162850725665026</v>
-      </c>
-      <c r="N12" s="286">
-        <v>1.197631452016424</v>
-      </c>
+      <c r="A12" s="256" t="s">
+        <v>37</v>
+      </c>
+      <c r="B12" s="313">
+        <v>0.22908459583548549</v>
+      </c>
+      <c r="C12" s="257">
+        <v>0.24153697929450549</v>
+      </c>
+      <c r="D12" s="258">
+        <v>0.2370655477661496</v>
+      </c>
+      <c r="E12" s="259">
+        <v>0.30961530375471508</v>
+      </c>
+      <c r="F12" s="260">
+        <v>0.15737053758770919</v>
+      </c>
+      <c r="G12" s="261">
+        <v>0.37609171456625679</v>
+      </c>
+      <c r="H12" s="263">
+        <v>1.3476954427810111</v>
+      </c>
+      <c r="I12" s="264">
+        <v>0.63517542340496691</v>
+      </c>
+      <c r="J12" s="262"/>
+      <c r="K12" s="263">
+        <v>0.3957859569434572</v>
+      </c>
+      <c r="L12" s="264">
+        <v>1.3257104736516481</v>
+      </c>
+      <c r="M12" s="257"/>
+      <c r="N12" s="265"/>
     </row>
     <row r="13" spans="1:14" ht="24.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="B13" s="344">
-        <v>0.1983994082899978</v>
-      </c>
-      <c r="C13" s="21"/>
-      <c r="D13" s="22">
-        <v>0.19460846787503569</v>
-      </c>
-      <c r="E13" s="127">
-        <v>0.26455684590571238</v>
-      </c>
-      <c r="F13" s="257"/>
-      <c r="G13" s="234">
-        <v>0.36579722539551929</v>
-      </c>
-      <c r="H13" s="217">
-        <v>1.1000469700288951</v>
-      </c>
-      <c r="I13" s="23">
-        <v>0.49634774464641912</v>
-      </c>
-      <c r="J13" s="200">
-        <v>0.25624918573318972</v>
-      </c>
-      <c r="K13" s="217">
-        <v>0.215602043539769</v>
-      </c>
-      <c r="L13" s="23">
-        <v>0.80565663736038395</v>
-      </c>
-      <c r="M13" s="21">
-        <v>0.26767540660082162</v>
-      </c>
-      <c r="N13" s="24">
-        <v>1.799130774503608</v>
-      </c>
+        <v>38</v>
+      </c>
+      <c r="B13" s="314">
+        <v>0.21078234798649029</v>
+      </c>
+      <c r="C13" s="20">
+        <v>0.23300354743836921</v>
+      </c>
+      <c r="D13" s="21">
+        <v>0.2114963981126288</v>
+      </c>
+      <c r="E13" s="124">
+        <v>0.26839585062955501</v>
+      </c>
+      <c r="F13" s="238">
+        <v>0.1641812758500707</v>
+      </c>
+      <c r="G13" s="219">
+        <v>0.29481824374251858</v>
+      </c>
+      <c r="H13" s="204"/>
+      <c r="I13" s="22">
+        <v>0.93853923353796587</v>
+      </c>
+      <c r="J13" s="189"/>
+      <c r="K13" s="204">
+        <v>0.18957354768572479</v>
+      </c>
+      <c r="L13" s="22">
+        <v>0.46026189081374791</v>
+      </c>
+      <c r="M13" s="20"/>
+      <c r="N13" s="23"/>
     </row>
     <row r="14" spans="1:14" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="16" t="s">
-        <v>26</v>
-      </c>
-      <c r="B14" s="342">
-        <v>0.1385445371911411</v>
-      </c>
-      <c r="C14" s="17"/>
-      <c r="D14" s="18">
-        <v>0.1243619738673085</v>
-      </c>
-      <c r="E14" s="126">
-        <v>0.12206994466738121</v>
-      </c>
-      <c r="F14" s="256"/>
-      <c r="G14" s="233">
-        <v>0.21199890466045179</v>
-      </c>
-      <c r="H14" s="216">
-        <v>0.70744095054907463</v>
-      </c>
-      <c r="I14" s="19">
-        <v>0.29387663876736642</v>
-      </c>
-      <c r="J14" s="199">
-        <v>0.1596593432079276</v>
-      </c>
-      <c r="K14" s="216">
-        <v>0.14127414611897809</v>
-      </c>
-      <c r="L14" s="19">
-        <v>0.52324874988781889</v>
-      </c>
-      <c r="M14" s="17">
-        <v>0.2508082317044753</v>
-      </c>
-      <c r="N14" s="20">
-        <v>0.3599396054199937</v>
-      </c>
+      <c r="A14" s="15" t="s">
+        <v>39</v>
+      </c>
+      <c r="B14" s="312">
+        <v>0.14316252825243539</v>
+      </c>
+      <c r="C14" s="16">
+        <v>0.15020682490168991</v>
+      </c>
+      <c r="D14" s="17">
+        <v>0.114102950828713</v>
+      </c>
+      <c r="E14" s="123">
+        <v>0.14316538275049509</v>
+      </c>
+      <c r="F14" s="237">
+        <v>0.1233501940448876</v>
+      </c>
+      <c r="G14" s="218">
+        <v>0.17980594018075241</v>
+      </c>
+      <c r="H14" s="203"/>
+      <c r="I14" s="18"/>
+      <c r="J14" s="188"/>
+      <c r="K14" s="203"/>
+      <c r="L14" s="18"/>
+      <c r="M14" s="16"/>
+      <c r="N14" s="19"/>
     </row>
     <row r="15" spans="1:14" ht="25.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="267" t="s">
-        <v>27</v>
-      </c>
-      <c r="B15" s="345">
-        <v>24.831620000000001</v>
-      </c>
-      <c r="C15" s="268">
-        <v>26.987309</v>
-      </c>
-      <c r="D15" s="269">
-        <v>28.120363000000001</v>
-      </c>
-      <c r="E15" s="270">
-        <v>34.067824999999999</v>
-      </c>
-      <c r="F15" s="271">
-        <v>44.099139999999998</v>
-      </c>
-      <c r="G15" s="272"/>
-      <c r="H15" s="274">
-        <v>46.092910000000003</v>
-      </c>
-      <c r="I15" s="275">
-        <v>33.037475999999998</v>
-      </c>
-      <c r="J15" s="273">
-        <v>34.180653</v>
-      </c>
-      <c r="K15" s="274">
-        <v>34.620643999999999</v>
-      </c>
-      <c r="L15" s="275">
-        <v>69.621340000000004</v>
-      </c>
-      <c r="M15" s="268">
-        <v>32.814259999999997</v>
-      </c>
-      <c r="N15" s="276">
-        <v>376.59089999999998</v>
+      <c r="A15" s="246" t="s">
+        <v>40</v>
+      </c>
+      <c r="B15" s="315">
+        <v>24.068906999999999</v>
+      </c>
+      <c r="C15" s="247">
+        <v>26.710523999999999</v>
+      </c>
+      <c r="D15" s="248">
+        <v>27.701635</v>
+      </c>
+      <c r="E15" s="249">
+        <v>34.611324000000003</v>
+      </c>
+      <c r="F15" s="250">
+        <v>26.08175</v>
+      </c>
+      <c r="G15" s="251"/>
+      <c r="H15" s="253">
+        <v>47.25056</v>
+      </c>
+      <c r="I15" s="254">
+        <v>43.801727</v>
+      </c>
+      <c r="J15" s="252">
+        <v>13.112904</v>
+      </c>
+      <c r="K15" s="253">
+        <v>34.852460000000001</v>
+      </c>
+      <c r="L15" s="254">
+        <v>28.748857000000001</v>
+      </c>
+      <c r="M15" s="247">
+        <v>5.0104164999999998</v>
+      </c>
+      <c r="N15" s="255">
+        <v>30.170214000000001</v>
       </c>
     </row>
     <row r="16" spans="1:14" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="25" t="s">
-        <v>28</v>
-      </c>
-      <c r="B16" s="346"/>
-      <c r="C16" s="26"/>
-      <c r="D16" s="27"/>
-      <c r="E16" s="128"/>
-      <c r="F16" s="258"/>
-      <c r="G16" s="235"/>
-      <c r="H16" s="218">
-        <v>24.598572000000001</v>
-      </c>
-      <c r="I16" s="28">
-        <v>29.766929999999999</v>
-      </c>
-      <c r="J16" s="201">
-        <v>25.57516</v>
-      </c>
-      <c r="K16" s="218">
-        <v>28.240639999999999</v>
-      </c>
-      <c r="L16" s="28">
-        <v>23.402363000000001</v>
-      </c>
-      <c r="M16" s="26">
-        <v>22.045421999999999</v>
-      </c>
-      <c r="N16" s="29">
-        <v>163.69958</v>
-      </c>
+      <c r="A16" s="24" t="s">
+        <v>41</v>
+      </c>
+      <c r="B16" s="316"/>
+      <c r="C16" s="25"/>
+      <c r="D16" s="26"/>
+      <c r="E16" s="125"/>
+      <c r="F16" s="239"/>
+      <c r="G16" s="220"/>
+      <c r="H16" s="205"/>
+      <c r="I16" s="27"/>
+      <c r="J16" s="190"/>
+      <c r="K16" s="205"/>
+      <c r="L16" s="27"/>
+      <c r="M16" s="25"/>
+      <c r="N16" s="28"/>
     </row>
     <row r="17" spans="1:15" ht="28.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A17" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="B17" s="347"/>
-      <c r="C17" s="30"/>
-      <c r="D17" s="31"/>
-      <c r="E17" s="129"/>
-      <c r="F17" s="259"/>
-      <c r="G17" s="236"/>
-      <c r="H17" s="219">
-        <v>24.526278000000001</v>
-      </c>
-      <c r="I17" s="32">
-        <v>10.491092999999999</v>
-      </c>
-      <c r="J17" s="202">
-        <v>12.15822</v>
-      </c>
-      <c r="K17" s="219">
-        <v>9.1702209999999997</v>
-      </c>
-      <c r="L17" s="32">
-        <v>24.697489999999998</v>
-      </c>
-      <c r="M17" s="30">
-        <v>8.235716</v>
-      </c>
-      <c r="N17" s="33">
-        <v>101.36520400000001</v>
-      </c>
+        <v>42</v>
+      </c>
+      <c r="B17" s="317"/>
+      <c r="C17" s="29"/>
+      <c r="D17" s="30"/>
+      <c r="E17" s="126"/>
+      <c r="F17" s="240"/>
+      <c r="G17" s="221"/>
+      <c r="H17" s="206"/>
+      <c r="I17" s="31">
+        <v>32.931694</v>
+      </c>
+      <c r="J17" s="191"/>
+      <c r="K17" s="206">
+        <v>12.900570999999999</v>
+      </c>
+      <c r="L17" s="31">
+        <v>14.824120499999999</v>
+      </c>
+      <c r="M17" s="29"/>
+      <c r="N17" s="32"/>
     </row>
     <row r="18" spans="1:15" ht="30.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="306" t="s">
-        <v>30</v>
-      </c>
-      <c r="B18" s="348"/>
-      <c r="C18" s="307"/>
-      <c r="D18" s="308"/>
-      <c r="E18" s="309"/>
-      <c r="F18" s="310"/>
-      <c r="G18" s="311"/>
-      <c r="H18" s="313" t="s">
-        <v>31</v>
-      </c>
-      <c r="I18" s="314" t="s">
-        <v>31</v>
-      </c>
-      <c r="J18" s="312" t="s">
-        <v>31</v>
-      </c>
-      <c r="K18" s="313" t="s">
-        <v>32</v>
-      </c>
-      <c r="L18" s="314" t="s">
-        <v>31</v>
-      </c>
-      <c r="M18" s="307" t="s">
-        <v>32</v>
-      </c>
-      <c r="N18" s="315" t="s">
-        <v>33</v>
-      </c>
+      <c r="A18" s="276" t="s">
+        <v>43</v>
+      </c>
+      <c r="B18" s="318"/>
+      <c r="C18" s="277"/>
+      <c r="D18" s="278"/>
+      <c r="E18" s="279"/>
+      <c r="F18" s="280"/>
+      <c r="G18" s="281"/>
+      <c r="H18" s="283"/>
+      <c r="I18" s="284" t="s">
+        <v>44</v>
+      </c>
+      <c r="J18" s="282"/>
+      <c r="K18" s="283" t="s">
+        <v>44</v>
+      </c>
+      <c r="L18" s="284" t="s">
+        <v>44</v>
+      </c>
+      <c r="M18" s="277"/>
+      <c r="N18" s="285"/>
     </row>
     <row r="19" spans="1:15" ht="30.6" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="179" t="s">
-        <v>34</v>
-      </c>
-      <c r="B19" s="349" t="s">
+      <c r="A19" s="172" t="s">
+        <v>45</v>
+      </c>
+      <c r="B19" s="319" t="s">
+        <v>46</v>
+      </c>
+      <c r="C19" s="173" t="s">
+        <v>47</v>
+      </c>
+      <c r="D19" s="174" t="s">
+        <v>46</v>
+      </c>
+      <c r="E19" s="175" t="s">
+        <v>47</v>
+      </c>
+      <c r="F19" s="241" t="s">
+        <v>47</v>
+      </c>
+      <c r="G19" s="222" t="s">
+        <v>46</v>
+      </c>
+      <c r="H19" s="207" t="s">
+        <v>47</v>
+      </c>
+      <c r="I19" s="181" t="s">
+        <v>47</v>
+      </c>
+      <c r="J19" s="192" t="s">
+        <v>47</v>
+      </c>
+      <c r="K19" s="207" t="s">
+        <v>47</v>
+      </c>
+      <c r="L19" s="181" t="s">
+        <v>47</v>
+      </c>
+      <c r="M19" s="173" t="s">
+        <v>47</v>
+      </c>
+      <c r="N19" s="176" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="139" t="s">
+        <v>48</v>
+      </c>
+      <c r="B20" s="320"/>
+      <c r="C20" s="140"/>
+      <c r="D20" s="141"/>
+      <c r="E20" s="227"/>
+      <c r="F20" s="242"/>
+      <c r="G20" s="223"/>
+      <c r="H20" s="208"/>
+      <c r="I20" s="142">
+        <v>73</v>
+      </c>
+      <c r="J20" s="193"/>
+      <c r="K20" s="208">
+        <v>17</v>
+      </c>
+      <c r="L20" s="142">
+        <v>22</v>
+      </c>
+      <c r="M20" s="140"/>
+      <c r="N20" s="143"/>
+    </row>
+    <row r="21" spans="1:15" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="161" t="s">
+        <v>49</v>
+      </c>
+      <c r="B21" s="321"/>
+      <c r="C21" s="135"/>
+      <c r="D21" s="136"/>
+      <c r="E21" s="228"/>
+      <c r="F21" s="243"/>
+      <c r="G21" s="224"/>
+      <c r="H21" s="209"/>
+      <c r="I21" s="137">
+        <v>62</v>
+      </c>
+      <c r="J21" s="194"/>
+      <c r="K21" s="209">
         <v>35</v>
       </c>
-      <c r="C19" s="180" t="s">
-        <v>35</v>
-      </c>
-      <c r="D19" s="181" t="s">
-        <v>35</v>
-      </c>
-      <c r="E19" s="182" t="s">
-        <v>36</v>
-      </c>
-      <c r="F19" s="260" t="s">
-        <v>36</v>
-      </c>
-      <c r="G19" s="237" t="s">
-        <v>35</v>
-      </c>
-      <c r="H19" s="220" t="s">
-        <v>36</v>
-      </c>
-      <c r="I19" s="192" t="s">
-        <v>36</v>
-      </c>
-      <c r="J19" s="203" t="s">
-        <v>36</v>
-      </c>
-      <c r="K19" s="220" t="s">
-        <v>36</v>
-      </c>
-      <c r="L19" s="192" t="s">
-        <v>36</v>
-      </c>
-      <c r="M19" s="180" t="s">
-        <v>36</v>
-      </c>
-      <c r="N19" s="183" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="20" spans="1:15" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="142" t="s">
-        <v>110</v>
-      </c>
-      <c r="B20" s="350"/>
-      <c r="C20" s="143"/>
-      <c r="D20" s="144"/>
-      <c r="E20" s="244"/>
-      <c r="F20" s="261"/>
-      <c r="G20" s="238"/>
-      <c r="H20" s="221"/>
-      <c r="I20" s="145"/>
-      <c r="J20" s="204"/>
-      <c r="K20" s="221"/>
-      <c r="L20" s="145"/>
-      <c r="M20" s="143"/>
-      <c r="N20" s="146"/>
-    </row>
-    <row r="21" spans="1:15" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="11" t="s">
-        <v>111</v>
-      </c>
-      <c r="B21" s="351"/>
-      <c r="C21" s="138"/>
-      <c r="D21" s="139"/>
-      <c r="E21" s="245"/>
-      <c r="F21" s="262"/>
-      <c r="G21" s="239"/>
-      <c r="H21" s="222"/>
-      <c r="I21" s="140"/>
-      <c r="J21" s="205"/>
-      <c r="K21" s="222"/>
-      <c r="L21" s="140"/>
-      <c r="M21" s="138"/>
-      <c r="N21" s="141"/>
+      <c r="L21" s="137">
+        <v>38</v>
+      </c>
+      <c r="M21" s="135"/>
+      <c r="N21" s="138"/>
     </row>
     <row r="22" spans="1:15" ht="22.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="325" t="s">
-        <v>112</v>
-      </c>
-      <c r="B22" s="352"/>
-      <c r="C22" s="326"/>
-      <c r="D22" s="327"/>
-      <c r="E22" s="328"/>
-      <c r="F22" s="329"/>
-      <c r="G22" s="330"/>
-      <c r="H22" s="332"/>
-      <c r="I22" s="333"/>
-      <c r="J22" s="331"/>
-      <c r="K22" s="332"/>
-      <c r="L22" s="333"/>
-      <c r="M22" s="326"/>
-      <c r="N22" s="334"/>
+      <c r="A22" s="295" t="s">
+        <v>50</v>
+      </c>
+      <c r="B22" s="322"/>
+      <c r="C22" s="296"/>
+      <c r="D22" s="297"/>
+      <c r="E22" s="298"/>
+      <c r="F22" s="299"/>
+      <c r="G22" s="300"/>
+      <c r="H22" s="302"/>
+      <c r="I22" s="303">
+        <v>135</v>
+      </c>
+      <c r="J22" s="301"/>
+      <c r="K22" s="302">
+        <v>52</v>
+      </c>
+      <c r="L22" s="303">
+        <v>60</v>
+      </c>
+      <c r="M22" s="296"/>
+      <c r="N22" s="304"/>
     </row>
     <row r="23" spans="1:15" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="142" t="s">
-        <v>117</v>
-      </c>
-      <c r="B23" s="353"/>
-      <c r="C23" s="287"/>
-      <c r="D23" s="288"/>
-      <c r="E23" s="289"/>
-      <c r="F23" s="290"/>
-      <c r="G23" s="291"/>
-      <c r="H23" s="293"/>
-      <c r="I23" s="294"/>
-      <c r="J23" s="292"/>
-      <c r="K23" s="293"/>
-      <c r="L23" s="294"/>
-      <c r="M23" s="287"/>
-      <c r="N23" s="295"/>
+      <c r="A23" s="139" t="s">
+        <v>51</v>
+      </c>
+      <c r="B23" s="323">
+        <v>68.5</v>
+      </c>
+      <c r="C23" s="266">
+        <v>73.5</v>
+      </c>
+      <c r="D23" s="267">
+        <v>69.3</v>
+      </c>
+      <c r="E23" s="268">
+        <v>72.8</v>
+      </c>
+      <c r="F23" s="269">
+        <v>69.2</v>
+      </c>
+      <c r="G23" s="270">
+        <v>42.8</v>
+      </c>
+      <c r="H23" s="272">
+        <v>65.2</v>
+      </c>
+      <c r="I23" s="273">
+        <v>56.6</v>
+      </c>
+      <c r="J23" s="271">
+        <v>52.1</v>
+      </c>
+      <c r="K23" s="272">
+        <v>89.2</v>
+      </c>
+      <c r="L23" s="273">
+        <v>73.8</v>
+      </c>
+      <c r="M23" s="266">
+        <v>65</v>
+      </c>
+      <c r="N23" s="274">
+        <v>39.6</v>
+      </c>
     </row>
     <row r="24" spans="1:15" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="168" t="s">
-        <v>113</v>
-      </c>
-      <c r="B24" s="354"/>
-      <c r="C24" s="147"/>
-      <c r="D24" s="148"/>
-      <c r="E24" s="246"/>
-      <c r="F24" s="263"/>
-      <c r="G24" s="240"/>
-      <c r="H24" s="223"/>
-      <c r="I24" s="149"/>
-      <c r="J24" s="206"/>
-      <c r="K24" s="223"/>
-      <c r="L24" s="149"/>
-      <c r="M24" s="147"/>
-      <c r="N24" s="150"/>
+      <c r="A24" s="161" t="s">
+        <v>52</v>
+      </c>
+      <c r="B24" s="324" t="s">
+        <v>53</v>
+      </c>
+      <c r="C24" s="144" t="s">
+        <v>54</v>
+      </c>
+      <c r="D24" s="145" t="s">
+        <v>53</v>
+      </c>
+      <c r="E24" s="229" t="s">
+        <v>54</v>
+      </c>
+      <c r="F24" s="244" t="s">
+        <v>53</v>
+      </c>
+      <c r="G24" s="225" t="s">
+        <v>55</v>
+      </c>
+      <c r="H24" s="210" t="s">
+        <v>53</v>
+      </c>
+      <c r="I24" s="146" t="s">
+        <v>53</v>
+      </c>
+      <c r="J24" s="195" t="s">
+        <v>53</v>
+      </c>
+      <c r="K24" s="210" t="s">
+        <v>54</v>
+      </c>
+      <c r="L24" s="146" t="s">
+        <v>54</v>
+      </c>
+      <c r="M24" s="144" t="s">
+        <v>53</v>
+      </c>
+      <c r="N24" s="147" t="s">
+        <v>55</v>
+      </c>
     </row>
     <row r="25" spans="1:15" ht="37.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="191" t="s">
-        <v>118</v>
-      </c>
-      <c r="B25" s="355"/>
-      <c r="C25" s="187"/>
-      <c r="D25" s="188"/>
-      <c r="E25" s="247"/>
-      <c r="F25" s="264"/>
-      <c r="G25" s="241"/>
-      <c r="H25" s="224"/>
-      <c r="I25" s="189"/>
-      <c r="J25" s="207"/>
-      <c r="K25" s="224"/>
-      <c r="L25" s="189"/>
-      <c r="M25" s="187"/>
-      <c r="N25" s="190"/>
+      <c r="A25" s="180" t="s">
+        <v>56</v>
+      </c>
+      <c r="B25" s="349" t="s">
+        <v>57</v>
+      </c>
+      <c r="C25" s="350" t="s">
+        <v>58</v>
+      </c>
+      <c r="D25" s="351" t="s">
+        <v>57</v>
+      </c>
+      <c r="E25" s="352" t="s">
+        <v>58</v>
+      </c>
+      <c r="F25" s="353" t="s">
+        <v>57</v>
+      </c>
+      <c r="G25" s="354" t="s">
+        <v>59</v>
+      </c>
+      <c r="H25" s="355" t="s">
+        <v>57</v>
+      </c>
+      <c r="I25" s="356" t="s">
+        <v>57</v>
+      </c>
+      <c r="J25" s="357" t="s">
+        <v>57</v>
+      </c>
+      <c r="K25" s="358" t="s">
+        <v>58</v>
+      </c>
+      <c r="L25" s="359" t="s">
+        <v>58</v>
+      </c>
+      <c r="M25" s="360" t="s">
+        <v>57</v>
+      </c>
+      <c r="N25" s="361" t="s">
+        <v>59</v>
+      </c>
     </row>
     <row r="26" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="151" t="s">
-        <v>115</v>
-      </c>
-      <c r="B26" s="356"/>
-      <c r="C26" s="152"/>
-      <c r="D26" s="153"/>
-      <c r="E26" s="248"/>
-      <c r="F26" s="265"/>
-      <c r="G26" s="242"/>
-      <c r="H26" s="225"/>
-      <c r="I26" s="154"/>
-      <c r="J26" s="208"/>
-      <c r="K26" s="225"/>
-      <c r="L26" s="154"/>
-      <c r="M26" s="152"/>
-      <c r="N26" s="155"/>
+      <c r="A26" s="148" t="s">
+        <v>60</v>
+      </c>
+      <c r="B26" s="325">
+        <v>93.41</v>
+      </c>
+      <c r="C26" s="149">
+        <v>105.4</v>
+      </c>
+      <c r="D26" s="150">
+        <v>59.27</v>
+      </c>
+      <c r="E26" s="230">
+        <v>53.2</v>
+      </c>
+      <c r="F26" s="245">
+        <v>89.75</v>
+      </c>
+      <c r="G26" s="226">
+        <v>24.94</v>
+      </c>
+      <c r="H26" s="211">
+        <v>48.41</v>
+      </c>
+      <c r="I26" s="151">
+        <v>30.24</v>
+      </c>
+      <c r="J26" s="196">
+        <v>11.28</v>
+      </c>
+      <c r="K26" s="211">
+        <v>28.23</v>
+      </c>
+      <c r="L26" s="151">
+        <v>27.09</v>
+      </c>
+      <c r="M26" s="149">
+        <v>6.83</v>
+      </c>
+      <c r="N26" s="152">
+        <v>42.48</v>
+      </c>
     </row>
     <row r="27" spans="1:15" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="157" t="s">
-        <v>116</v>
-      </c>
-      <c r="B27" s="357"/>
-      <c r="C27" s="158"/>
-      <c r="D27" s="159"/>
-      <c r="E27" s="249"/>
-      <c r="F27" s="266"/>
-      <c r="G27" s="243"/>
-      <c r="H27" s="226"/>
-      <c r="I27" s="160"/>
-      <c r="J27" s="209"/>
-      <c r="K27" s="226"/>
-      <c r="L27" s="160"/>
-      <c r="M27" s="158"/>
-      <c r="N27" s="161"/>
-      <c r="O27" s="156"/>
+      <c r="A27" s="154" t="s">
+        <v>61</v>
+      </c>
+      <c r="B27" s="362">
+        <v>119.25</v>
+      </c>
+      <c r="C27" s="363">
+        <v>136.94</v>
+      </c>
+      <c r="D27" s="364">
+        <v>75.760000000000005</v>
+      </c>
+      <c r="E27" s="365">
+        <v>72.2</v>
+      </c>
+      <c r="F27" s="366">
+        <v>107.86</v>
+      </c>
+      <c r="G27" s="367">
+        <v>41.47</v>
+      </c>
+      <c r="H27" s="368">
+        <v>126.57</v>
+      </c>
+      <c r="I27" s="369">
+        <v>53.03</v>
+      </c>
+      <c r="J27" s="370">
+        <v>16.82</v>
+      </c>
+      <c r="K27" s="368">
+        <v>42.52</v>
+      </c>
+      <c r="L27" s="369">
+        <v>64</v>
+      </c>
+      <c r="M27" s="371">
+        <v>10.24</v>
+      </c>
+      <c r="N27" s="372">
+        <v>78.33</v>
+      </c>
+      <c r="O27" s="153"/>
     </row>
     <row r="28" spans="1:15" ht="34.200000000000003" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="296" t="s">
-        <v>124</v>
-      </c>
-      <c r="B28" s="358"/>
-      <c r="C28" s="297"/>
-      <c r="D28" s="298"/>
-      <c r="E28" s="299"/>
-      <c r="F28" s="300"/>
-      <c r="G28" s="301"/>
-      <c r="H28" s="303"/>
-      <c r="I28" s="304"/>
-      <c r="J28" s="302"/>
-      <c r="K28" s="303"/>
-      <c r="L28" s="304"/>
-      <c r="M28" s="297"/>
-      <c r="N28" s="305"/>
-    </row>
-    <row r="29" spans="1:15" ht="15" thickTop="1" x14ac:dyDescent="0.3"/>
+      <c r="A28" s="275" t="s">
+        <v>62</v>
+      </c>
+      <c r="B28" s="373">
+        <v>75.2</v>
+      </c>
+      <c r="C28" s="374">
+        <v>77.7</v>
+      </c>
+      <c r="D28" s="375">
+        <v>76.7</v>
+      </c>
+      <c r="E28" s="376">
+        <v>80.2</v>
+      </c>
+      <c r="F28" s="377">
+        <v>77.3</v>
+      </c>
+      <c r="G28" s="378">
+        <v>54</v>
+      </c>
+      <c r="H28" s="379">
+        <v>82</v>
+      </c>
+      <c r="I28" s="380">
+        <v>61.9</v>
+      </c>
+      <c r="J28" s="381">
+        <v>63.9</v>
+      </c>
+      <c r="K28" s="379">
+        <v>73.900000000000006</v>
+      </c>
+      <c r="L28" s="380">
+        <v>63</v>
+      </c>
+      <c r="M28" s="382">
+        <v>60</v>
+      </c>
+      <c r="N28" s="383">
+        <v>61.4</v>
+      </c>
+    </row>
+    <row r="29" spans="1:15" ht="15" customHeight="1" thickTop="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <conditionalFormatting sqref="B18:E18 H18:N18">
     <cfRule type="expression" dxfId="38" priority="31">
@@ -5247,8 +5184,6 @@
     <cfRule type="expression" dxfId="5" priority="46" stopIfTrue="1">
       <formula>AND(B15&lt;&gt;"",B15&gt;100)</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B15:N15">
     <cfRule type="expression" dxfId="4" priority="47" stopIfTrue="1">
       <formula>AND(B15&lt;&gt;"",B15&gt;=50,B15&lt;100)</formula>
     </cfRule>
@@ -5257,8 +5192,6 @@
     <cfRule type="expression" dxfId="3" priority="48" stopIfTrue="1">
       <formula>AND(B16&lt;&gt;"",B16&gt;100)</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B16:N16">
     <cfRule type="expression" dxfId="2" priority="49" stopIfTrue="1">
       <formula>AND(B16&lt;&gt;"",B16&gt;=50,B16&lt;100)</formula>
     </cfRule>
@@ -5267,8 +5200,6 @@
     <cfRule type="expression" dxfId="1" priority="50" stopIfTrue="1">
       <formula>AND(B17&lt;&gt;"",B17&gt;100)</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B17:N17">
     <cfRule type="expression" dxfId="0" priority="51" stopIfTrue="1">
       <formula>AND(B17&lt;&gt;"",B17&gt;=50,B17&lt;100)</formula>
     </cfRule>
@@ -5289,77 +5220,77 @@
   <dimension ref="A1:A29"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="18.33203125" style="40" customWidth="1"/>
+    <col min="1" max="1" width="18.33203125" style="39" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:1" ht="19.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="52" t="s">
-        <v>37</v>
+      <c r="A1" s="51" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="2" spans="1:1" ht="19.95" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3" spans="1:1" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>132</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:1" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
     </row>
     <row r="5" spans="1:1" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
     </row>
     <row r="6" spans="1:1" ht="19.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>96</v>
+        <v>20</v>
       </c>
     </row>
     <row r="7" spans="1:1" ht="19.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>136</v>
+        <v>21</v>
       </c>
     </row>
     <row r="8" spans="1:1" ht="19.95" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>137</v>
+        <v>22</v>
       </c>
     </row>
     <row r="9" spans="1:1" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
     </row>
     <row r="10" spans="1:1" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>139</v>
+        <v>24</v>
       </c>
     </row>
     <row r="11" spans="1:1" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>140</v>
+        <v>25</v>
       </c>
     </row>
     <row r="12" spans="1:1" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>141</v>
+        <v>26</v>
       </c>
     </row>
     <row r="13" spans="1:1" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>142</v>
+        <v>27</v>
       </c>
     </row>
     <row r="14" spans="1:1" ht="19.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>144</v>
+        <v>28</v>
       </c>
     </row>
     <row r="15" spans="1:1" ht="15" customHeight="1" thickTop="1" x14ac:dyDescent="0.3"/>
@@ -5387,128 +5318,128 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="53" t="s">
-        <v>38</v>
+      <c r="A1" s="52" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="2" spans="1:1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="54"/>
+      <c r="A2" s="53"/>
     </row>
     <row r="3" spans="1:1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="55" t="s">
-        <v>39</v>
+      <c r="A3" s="54" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="4" spans="1:1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="54" t="s">
-        <v>119</v>
+      <c r="A4" s="53" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="5" spans="1:1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="54" t="s">
-        <v>120</v>
+      <c r="A5" s="53" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="6" spans="1:1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="54" t="s">
-        <v>121</v>
+      <c r="A6" s="53" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="7" spans="1:1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="54" t="s">
-        <v>40</v>
+      <c r="A7" s="53" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="8" spans="1:1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="54"/>
+      <c r="A8" s="53"/>
     </row>
     <row r="9" spans="1:1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="55" t="s">
-        <v>114</v>
+      <c r="A9" s="54" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="10" spans="1:1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="54"/>
+      <c r="A10" s="53"/>
     </row>
     <row r="11" spans="1:1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="55" t="s">
-        <v>41</v>
+      <c r="A11" s="54" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="12" spans="1:1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="54" t="s">
-        <v>42</v>
+      <c r="A12" s="53" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="13" spans="1:1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="54" t="s">
-        <v>43</v>
+      <c r="A13" s="53" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="14" spans="1:1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="55" t="s">
-        <v>122</v>
+      <c r="A14" s="54" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="15" spans="1:1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="54"/>
+      <c r="A15" s="53"/>
     </row>
     <row r="16" spans="1:1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="55" t="s">
-        <v>44</v>
+      <c r="A16" s="54" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="17" spans="1:1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="54" t="s">
-        <v>45</v>
+      <c r="A17" s="53" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="18" spans="1:1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="55" t="s">
-        <v>123</v>
+      <c r="A18" s="54" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="19" spans="1:1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="54" t="s">
-        <v>46</v>
+      <c r="A19" s="53" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="20" spans="1:1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="54"/>
+      <c r="A20" s="53"/>
     </row>
     <row r="21" spans="1:1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="55" t="s">
-        <v>47</v>
+      <c r="A21" s="54" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="22" spans="1:1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="53" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="24" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A24" s="55" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="25" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A25" s="55" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="26" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A26" s="54" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="27" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A27" s="55" t="s">
-        <v>109</v>
+      <c r="A22" s="52" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="54" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="54" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="53" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="54" t="s">
+        <v>84</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="5" orientation="landscape" r:id="rId1"/>
+  <pageSetup paperSize="5" orientation="landscape"/>
 </worksheet>
 </file>
 
@@ -5520,222 +5451,222 @@
   <dimension ref="A1:C32"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="241" style="40" customWidth="1"/>
+    <col min="1" max="1" width="241" style="39" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="37.799999999999997" customHeight="1" thickTop="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="7" t="s">
-        <v>49</v>
+        <v>85</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="3"/>
     </row>
     <row r="2" spans="1:3" ht="40.200000000000003" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" s="41" t="s">
-        <v>50</v>
+      <c r="A2" s="40" t="s">
+        <v>86</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="3"/>
     </row>
     <row r="3" spans="1:3" ht="40.799999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A3" s="41" t="s">
-        <v>51</v>
+      <c r="A3" s="40" t="s">
+        <v>87</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" s="3"/>
     </row>
     <row r="4" spans="1:3" ht="33" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A4" s="42" t="s">
-        <v>52</v>
+      <c r="A4" s="41" t="s">
+        <v>88</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" s="3"/>
     </row>
     <row r="5" spans="1:3" ht="33" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A5" s="43" t="s">
-        <v>53</v>
+      <c r="A5" s="42" t="s">
+        <v>89</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="3"/>
     </row>
     <row r="6" spans="1:3" ht="34.799999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A6" s="43" t="s">
-        <v>54</v>
+      <c r="A6" s="42" t="s">
+        <v>90</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" s="3"/>
     </row>
     <row r="7" spans="1:3" ht="32.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A7" s="43" t="s">
-        <v>55</v>
+      <c r="A7" s="42" t="s">
+        <v>91</v>
       </c>
       <c r="B7" s="2"/>
       <c r="C7" s="3"/>
     </row>
     <row r="8" spans="1:3" ht="37.200000000000003" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A8" s="43" t="s">
-        <v>56</v>
+      <c r="A8" s="42" t="s">
+        <v>92</v>
       </c>
       <c r="B8" s="2"/>
       <c r="C8" s="3"/>
     </row>
     <row r="9" spans="1:3" ht="35.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A9" s="43" t="s">
-        <v>57</v>
+      <c r="A9" s="42" t="s">
+        <v>93</v>
       </c>
       <c r="B9" s="2"/>
       <c r="C9" s="3"/>
     </row>
     <row r="10" spans="1:3" ht="37.200000000000003" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A10" s="43" t="s">
-        <v>58</v>
+      <c r="A10" s="42" t="s">
+        <v>94</v>
       </c>
       <c r="B10" s="2"/>
       <c r="C10" s="3"/>
     </row>
     <row r="11" spans="1:3" ht="37.799999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A11" s="44" t="s">
-        <v>130</v>
+      <c r="A11" s="43" t="s">
+        <v>95</v>
       </c>
       <c r="B11" s="2"/>
       <c r="C11" s="3"/>
     </row>
     <row r="12" spans="1:3" ht="34.799999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A12" s="43" t="s">
-        <v>125</v>
+      <c r="A12" s="42" t="s">
+        <v>96</v>
       </c>
       <c r="B12" s="2"/>
       <c r="C12" s="3"/>
     </row>
     <row r="13" spans="1:3" ht="36.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A13" s="43" t="s">
-        <v>59</v>
+      <c r="A13" s="42" t="s">
+        <v>97</v>
       </c>
       <c r="B13" s="2"/>
       <c r="C13" s="3"/>
     </row>
     <row r="14" spans="1:3" ht="33" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A14" s="43" t="s">
-        <v>126</v>
+      <c r="A14" s="42" t="s">
+        <v>98</v>
       </c>
       <c r="B14" s="2"/>
       <c r="C14" s="3"/>
     </row>
     <row r="15" spans="1:3" ht="33.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A15" s="43" t="s">
-        <v>60</v>
+      <c r="A15" s="42" t="s">
+        <v>99</v>
       </c>
       <c r="B15" s="2"/>
       <c r="C15" s="3"/>
     </row>
     <row r="16" spans="1:3" ht="33.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A16" s="43" t="s">
-        <v>61</v>
+      <c r="A16" s="42" t="s">
+        <v>100</v>
       </c>
       <c r="B16" s="2"/>
       <c r="C16" s="3"/>
     </row>
     <row r="17" spans="1:3" ht="37.200000000000003" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A17" s="43" t="s">
-        <v>62</v>
+      <c r="A17" s="42" t="s">
+        <v>101</v>
       </c>
       <c r="B17" s="2"/>
       <c r="C17" s="3"/>
     </row>
     <row r="18" spans="1:3" ht="39" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A18" s="44" t="s">
-        <v>63</v>
+      <c r="A18" s="43" t="s">
+        <v>102</v>
       </c>
       <c r="B18" s="2"/>
       <c r="C18" s="3"/>
     </row>
     <row r="19" spans="1:3" ht="35.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A19" s="43" t="s">
-        <v>64</v>
+      <c r="A19" s="42" t="s">
+        <v>103</v>
       </c>
       <c r="B19" s="2"/>
       <c r="C19" s="3"/>
     </row>
     <row r="20" spans="1:3" ht="39" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A20" s="43" t="s">
-        <v>65</v>
+      <c r="A20" s="42" t="s">
+        <v>104</v>
       </c>
       <c r="B20" s="2"/>
       <c r="C20" s="3"/>
     </row>
     <row r="21" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A21" s="45" t="s">
-        <v>66</v>
+      <c r="A21" s="44" t="s">
+        <v>105</v>
       </c>
       <c r="B21" s="2"/>
       <c r="C21" s="3"/>
     </row>
     <row r="22" spans="1:3" ht="180" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A22" s="46" t="s">
-        <v>127</v>
+      <c r="A22" s="45" t="s">
+        <v>106</v>
       </c>
       <c r="B22" s="2"/>
       <c r="C22" s="3"/>
     </row>
     <row r="23" spans="1:3" ht="28.8" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A23" s="47" t="s">
-        <v>67</v>
+      <c r="A23" s="46" t="s">
+        <v>107</v>
       </c>
       <c r="B23" s="2"/>
       <c r="C23" s="3"/>
     </row>
     <row r="24" spans="1:3" ht="182.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A24" s="46" t="s">
-        <v>128</v>
+      <c r="A24" s="45" t="s">
+        <v>108</v>
       </c>
       <c r="B24" s="2"/>
       <c r="C24" s="3"/>
     </row>
     <row r="25" spans="1:3" ht="31.8" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A25" s="48" t="s">
-        <v>68</v>
+      <c r="A25" s="47" t="s">
+        <v>109</v>
       </c>
       <c r="B25" s="2"/>
       <c r="C25" s="3"/>
     </row>
     <row r="26" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A26" s="46" t="s">
-        <v>69</v>
+      <c r="A26" s="45" t="s">
+        <v>110</v>
       </c>
       <c r="B26" s="2"/>
       <c r="C26" s="3"/>
     </row>
     <row r="27" spans="1:3" ht="30.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A27" s="49" t="s">
-        <v>129</v>
+      <c r="A27" s="48" t="s">
+        <v>111</v>
       </c>
       <c r="B27" s="2"/>
       <c r="C27" s="3"/>
     </row>
     <row r="28" spans="1:3" ht="67.2" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A28" s="46" t="s">
-        <v>70</v>
+      <c r="A28" s="45" t="s">
+        <v>112</v>
       </c>
       <c r="B28" s="2"/>
       <c r="C28" s="3"/>
     </row>
     <row r="29" spans="1:3" ht="34.200000000000003" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A29" s="46" t="s">
-        <v>71</v>
+      <c r="A29" s="45" t="s">
+        <v>113</v>
       </c>
       <c r="B29" s="2"/>
       <c r="C29" s="3"/>
     </row>
     <row r="30" spans="1:3" ht="41.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A30" s="50" t="s">
-        <v>72</v>
+      <c r="A30" s="49" t="s">
+        <v>114</v>
       </c>
       <c r="B30" s="2"/>
       <c r="C30" s="3"/>
     </row>
     <row r="31" spans="1:3" ht="33.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A31" s="51" t="s">
-        <v>73</v>
+      <c r="A31" s="50" t="s">
+        <v>115</v>
       </c>
       <c r="B31" s="2"/>
       <c r="C31" s="3"/>
@@ -5751,450 +5682,450 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BEE767CC-D45C-4197-9647-33512F98A8EE}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <sheetPr codeName="Sheet5">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:K25"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="20.77734375" customWidth="1"/>
-    <col min="2" max="2" width="23" customWidth="1"/>
-    <col min="3" max="3" width="20.77734375" customWidth="1"/>
-    <col min="4" max="4" width="2.77734375" customWidth="1"/>
-    <col min="5" max="5" width="20.77734375" customWidth="1"/>
-    <col min="6" max="6" width="2.77734375" customWidth="1"/>
-    <col min="7" max="7" width="26.33203125" customWidth="1"/>
-    <col min="8" max="8" width="28.88671875" customWidth="1"/>
-    <col min="9" max="9" width="2.77734375" customWidth="1"/>
-    <col min="10" max="10" width="23.6640625" customWidth="1"/>
-    <col min="11" max="11" width="29.109375" customWidth="1"/>
+    <col min="1" max="1" width="20.77734375" style="4" customWidth="1"/>
+    <col min="2" max="2" width="23" style="4" customWidth="1"/>
+    <col min="3" max="3" width="20.77734375" style="4" customWidth="1"/>
+    <col min="4" max="4" width="2.77734375" style="4" customWidth="1"/>
+    <col min="5" max="5" width="20.77734375" style="4" customWidth="1"/>
+    <col min="6" max="6" width="2.77734375" style="4" customWidth="1"/>
+    <col min="7" max="7" width="26.33203125" style="4" customWidth="1"/>
+    <col min="8" max="8" width="28.88671875" style="4" customWidth="1"/>
+    <col min="9" max="9" width="2.77734375" style="4" customWidth="1"/>
+    <col min="10" max="10" width="23.6640625" style="4" customWidth="1"/>
+    <col min="11" max="11" width="29.109375" style="4" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="25.8" x14ac:dyDescent="0.3">
-      <c r="A1" s="135" t="s">
-        <v>74</v>
-      </c>
-      <c r="B1" s="56"/>
-      <c r="C1" s="56"/>
-      <c r="D1" s="56"/>
-      <c r="E1" s="56"/>
-      <c r="F1" s="56"/>
-      <c r="G1" s="56"/>
-      <c r="H1" s="56"/>
-      <c r="I1" s="56"/>
-      <c r="J1" s="56"/>
-      <c r="K1" s="56"/>
-    </row>
-    <row r="2" spans="1:11" ht="21" x14ac:dyDescent="0.3">
-      <c r="A2" s="136" t="s">
-        <v>88</v>
-      </c>
-      <c r="B2" s="58"/>
-      <c r="C2" s="57"/>
-      <c r="D2" s="57"/>
-      <c r="E2" s="57"/>
-      <c r="F2" s="57"/>
-      <c r="G2" s="57"/>
-      <c r="H2" s="57"/>
-      <c r="I2" s="57"/>
-      <c r="J2" s="57"/>
-      <c r="K2" s="57"/>
+    <row r="1" spans="1:11" ht="25.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="132" t="s">
+        <v>116</v>
+      </c>
+      <c r="B1" s="55"/>
+      <c r="C1" s="55"/>
+      <c r="D1" s="55"/>
+      <c r="E1" s="55"/>
+      <c r="F1" s="55"/>
+      <c r="G1" s="55"/>
+      <c r="H1" s="55"/>
+      <c r="I1" s="55"/>
+      <c r="J1" s="55"/>
+      <c r="K1" s="55"/>
+    </row>
+    <row r="2" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="133" t="s">
+        <v>117</v>
+      </c>
+      <c r="B2" s="57"/>
+      <c r="C2" s="56"/>
+      <c r="D2" s="56"/>
+      <c r="E2" s="56"/>
+      <c r="F2" s="56"/>
+      <c r="G2" s="56"/>
+      <c r="H2" s="56"/>
+      <c r="I2" s="56"/>
+      <c r="J2" s="56"/>
+      <c r="K2" s="56"/>
     </row>
     <row r="3" spans="1:11" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="57"/>
-      <c r="B3" s="57"/>
-      <c r="C3" s="57"/>
-      <c r="D3" s="57"/>
-      <c r="E3" s="57"/>
-      <c r="F3" s="57"/>
-      <c r="G3" s="57"/>
-      <c r="H3" s="57"/>
-      <c r="I3" s="57"/>
-      <c r="J3" s="57"/>
-      <c r="K3" s="57"/>
+      <c r="A3" s="56"/>
+      <c r="B3" s="56"/>
+      <c r="C3" s="56"/>
+      <c r="D3" s="56"/>
+      <c r="E3" s="56"/>
+      <c r="F3" s="56"/>
+      <c r="G3" s="56"/>
+      <c r="H3" s="56"/>
+      <c r="I3" s="56"/>
+      <c r="J3" s="56"/>
+      <c r="K3" s="56"/>
     </row>
     <row r="4" spans="1:11" ht="81" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="59" t="s">
-        <v>75</v>
-      </c>
-      <c r="B4" s="60" t="s">
-        <v>76</v>
-      </c>
-      <c r="C4" s="61" t="s">
-        <v>77</v>
-      </c>
-      <c r="D4" s="62"/>
-      <c r="E4" s="63" t="s">
-        <v>89</v>
-      </c>
-      <c r="F4" s="64"/>
-      <c r="G4" s="65" t="s">
-        <v>91</v>
-      </c>
-      <c r="H4" s="66" t="s">
-        <v>93</v>
-      </c>
-      <c r="I4" s="67"/>
-      <c r="J4" s="89" t="s">
-        <v>92</v>
-      </c>
-      <c r="K4" s="90" t="s">
-        <v>94</v>
+      <c r="A4" s="58" t="s">
+        <v>118</v>
+      </c>
+      <c r="B4" s="59" t="s">
+        <v>119</v>
+      </c>
+      <c r="C4" s="60" t="s">
+        <v>120</v>
+      </c>
+      <c r="D4" s="61"/>
+      <c r="E4" s="62" t="s">
+        <v>121</v>
+      </c>
+      <c r="F4" s="63"/>
+      <c r="G4" s="64" t="s">
+        <v>122</v>
+      </c>
+      <c r="H4" s="65" t="s">
+        <v>123</v>
+      </c>
+      <c r="I4" s="66"/>
+      <c r="J4" s="87" t="s">
+        <v>124</v>
+      </c>
+      <c r="K4" s="88" t="s">
+        <v>125</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="32.4" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="97">
+      <c r="A5" s="95">
         <v>1</v>
       </c>
-      <c r="B5" s="98">
+      <c r="B5" s="96">
         <v>0.05</v>
       </c>
-      <c r="C5" s="99" t="s">
-        <v>78</v>
-      </c>
-      <c r="D5" s="100"/>
-      <c r="E5" s="101" t="s">
-        <v>79</v>
-      </c>
-      <c r="F5" s="102"/>
-      <c r="G5" s="103" t="s">
-        <v>80</v>
-      </c>
-      <c r="H5" s="104">
+      <c r="C5" s="97" t="s">
+        <v>126</v>
+      </c>
+      <c r="D5" s="98"/>
+      <c r="E5" s="99" t="s">
+        <v>127</v>
+      </c>
+      <c r="F5" s="100"/>
+      <c r="G5" s="101" t="s">
+        <v>128</v>
+      </c>
+      <c r="H5" s="102">
         <v>0.2</v>
       </c>
-      <c r="I5" s="105"/>
-      <c r="J5" s="106" t="s">
-        <v>81</v>
-      </c>
-      <c r="K5" s="107">
+      <c r="I5" s="103"/>
+      <c r="J5" s="104" t="s">
+        <v>129</v>
+      </c>
+      <c r="K5" s="105">
         <v>0.4</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="25.2" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="108">
+      <c r="A6" s="106">
         <v>2</v>
       </c>
-      <c r="B6" s="109">
+      <c r="B6" s="107">
         <v>0.1</v>
       </c>
-      <c r="C6" s="110" t="s">
-        <v>82</v>
-      </c>
-      <c r="D6" s="111"/>
-      <c r="E6" s="112" t="s">
-        <v>80</v>
-      </c>
-      <c r="F6" s="113"/>
-      <c r="G6" s="114" t="s">
-        <v>80</v>
-      </c>
-      <c r="H6" s="115">
+      <c r="C6" s="108" t="s">
+        <v>130</v>
+      </c>
+      <c r="D6" s="109"/>
+      <c r="E6" s="110" t="s">
+        <v>128</v>
+      </c>
+      <c r="F6" s="111"/>
+      <c r="G6" s="112" t="s">
+        <v>128</v>
+      </c>
+      <c r="H6" s="113">
         <v>0.1</v>
       </c>
-      <c r="I6" s="116"/>
-      <c r="J6" s="117" t="s">
-        <v>81</v>
-      </c>
-      <c r="K6" s="118">
+      <c r="I6" s="114"/>
+      <c r="J6" s="115" t="s">
+        <v>129</v>
+      </c>
+      <c r="K6" s="116">
         <v>0.2</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="22.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="68">
+      <c r="A7" s="67">
         <v>3</v>
       </c>
-      <c r="B7" s="88">
+      <c r="B7" s="86">
         <v>0.15</v>
       </c>
-      <c r="C7" s="86" t="s">
-        <v>83</v>
-      </c>
-      <c r="D7" s="69"/>
-      <c r="E7" s="70" t="s">
-        <v>84</v>
-      </c>
-      <c r="F7" s="71"/>
-      <c r="G7" s="72" t="s">
-        <v>80</v>
-      </c>
-      <c r="H7" s="73" t="s">
-        <v>85</v>
-      </c>
-      <c r="I7" s="74"/>
-      <c r="J7" s="95" t="s">
-        <v>81</v>
-      </c>
-      <c r="K7" s="91" t="s">
-        <v>86</v>
+      <c r="C7" s="84" t="s">
+        <v>131</v>
+      </c>
+      <c r="D7" s="68"/>
+      <c r="E7" s="69" t="s">
+        <v>132</v>
+      </c>
+      <c r="F7" s="70"/>
+      <c r="G7" s="71" t="s">
+        <v>128</v>
+      </c>
+      <c r="H7" s="72" t="s">
+        <v>133</v>
+      </c>
+      <c r="I7" s="73"/>
+      <c r="J7" s="93" t="s">
+        <v>129</v>
+      </c>
+      <c r="K7" s="89" t="s">
+        <v>134</v>
       </c>
     </row>
     <row r="8" spans="1:11" ht="25.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="75">
+      <c r="A8" s="74">
         <v>4</v>
       </c>
-      <c r="B8" s="137">
+      <c r="B8" s="134">
         <v>0.2</v>
       </c>
-      <c r="C8" s="87" t="s">
-        <v>87</v>
-      </c>
-      <c r="D8" s="76"/>
-      <c r="E8" s="77" t="s">
-        <v>81</v>
-      </c>
-      <c r="F8" s="78"/>
-      <c r="G8" s="79" t="s">
-        <v>80</v>
-      </c>
-      <c r="H8" s="80">
+      <c r="C8" s="85" t="s">
+        <v>135</v>
+      </c>
+      <c r="D8" s="75"/>
+      <c r="E8" s="76" t="s">
+        <v>129</v>
+      </c>
+      <c r="F8" s="77"/>
+      <c r="G8" s="78" t="s">
+        <v>128</v>
+      </c>
+      <c r="H8" s="79">
         <v>0.05</v>
       </c>
-      <c r="I8" s="81"/>
-      <c r="J8" s="96" t="s">
-        <v>81</v>
-      </c>
-      <c r="K8" s="92">
+      <c r="I8" s="80"/>
+      <c r="J8" s="94" t="s">
+        <v>129</v>
+      </c>
+      <c r="K8" s="90">
         <v>0.1</v>
       </c>
     </row>
-    <row r="9" spans="1:11" ht="15" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="82"/>
-      <c r="B9" s="82"/>
-      <c r="C9" s="82"/>
-      <c r="D9" s="82"/>
-      <c r="E9" s="82"/>
-      <c r="F9" s="82"/>
-      <c r="G9" s="82"/>
-      <c r="H9" s="82"/>
-      <c r="I9" s="82"/>
-      <c r="J9" s="82"/>
-      <c r="K9" s="82"/>
-    </row>
-    <row r="10" spans="1:11" s="4" customFormat="1" ht="21" x14ac:dyDescent="0.4">
-      <c r="A10" s="133" t="s">
-        <v>97</v>
-      </c>
-      <c r="B10" s="85"/>
-      <c r="C10" s="85"/>
-      <c r="D10" s="85"/>
-      <c r="E10" s="85"/>
-      <c r="F10" s="85"/>
-      <c r="G10" s="85"/>
-      <c r="H10" s="82"/>
-      <c r="I10" s="82"/>
-      <c r="J10" s="82"/>
-      <c r="K10" s="82"/>
-    </row>
-    <row r="11" spans="1:11" s="4" customFormat="1" ht="18" x14ac:dyDescent="0.35">
-      <c r="A11" s="130" t="s">
-        <v>99</v>
-      </c>
-      <c r="B11" s="130"/>
-      <c r="C11" s="130"/>
-      <c r="D11" s="130"/>
-      <c r="E11" s="130"/>
-      <c r="F11" s="130"/>
-      <c r="G11" s="130"/>
-      <c r="H11" s="134"/>
-      <c r="I11" s="82"/>
-      <c r="J11" s="82"/>
-      <c r="K11" s="82"/>
-    </row>
-    <row r="12" spans="1:11" s="4" customFormat="1" ht="18" x14ac:dyDescent="0.35">
-      <c r="A12" s="131" t="s">
-        <v>100</v>
-      </c>
-      <c r="B12" s="131"/>
-      <c r="C12" s="131"/>
-      <c r="D12" s="131"/>
-      <c r="E12" s="131"/>
-      <c r="F12" s="131"/>
-      <c r="G12" s="131"/>
-      <c r="H12" s="134"/>
-      <c r="I12" s="82"/>
-      <c r="J12" s="82"/>
-      <c r="K12" s="82"/>
-    </row>
-    <row r="13" spans="1:11" s="4" customFormat="1" ht="18" x14ac:dyDescent="0.35">
-      <c r="A13" s="132" t="s">
-        <v>101</v>
-      </c>
-      <c r="B13" s="132"/>
-      <c r="C13" s="132"/>
-      <c r="D13" s="132"/>
-      <c r="E13" s="132"/>
-      <c r="F13" s="132"/>
-      <c r="G13" s="132"/>
-      <c r="H13" s="134"/>
-      <c r="I13" s="82"/>
-      <c r="J13" s="82"/>
-      <c r="K13" s="82"/>
-    </row>
-    <row r="14" spans="1:11" s="4" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="82"/>
-      <c r="B14" s="82"/>
-      <c r="C14" s="82"/>
-      <c r="D14" s="82"/>
-      <c r="E14" s="82"/>
-      <c r="F14" s="82"/>
-      <c r="G14" s="82"/>
-      <c r="H14" s="82"/>
-      <c r="I14" s="82"/>
-      <c r="J14" s="82"/>
-      <c r="K14" s="82"/>
-    </row>
-    <row r="15" spans="1:11" ht="18" x14ac:dyDescent="0.35">
-      <c r="A15" s="83" t="s">
-        <v>90</v>
-      </c>
-      <c r="B15" s="84"/>
-      <c r="C15" s="84"/>
-      <c r="D15" s="84"/>
-      <c r="E15" s="84"/>
-      <c r="F15" s="84"/>
-      <c r="G15" s="84"/>
-      <c r="H15" s="82"/>
-      <c r="I15" s="82"/>
-      <c r="J15" s="82"/>
-      <c r="K15" s="82"/>
-    </row>
-    <row r="16" spans="1:11" ht="18" x14ac:dyDescent="0.35">
-      <c r="A16" s="85" t="s">
-        <v>102</v>
-      </c>
-      <c r="B16" s="85"/>
-      <c r="C16" s="85"/>
-      <c r="D16" s="85"/>
-      <c r="E16" s="85"/>
-      <c r="F16" s="85"/>
-      <c r="G16" s="85"/>
-      <c r="H16" s="82"/>
-      <c r="I16" s="82"/>
-      <c r="J16" s="82"/>
-      <c r="K16" s="82"/>
-    </row>
-    <row r="17" spans="1:11" ht="18" x14ac:dyDescent="0.35">
-      <c r="A17" s="85" t="s">
-        <v>103</v>
-      </c>
-      <c r="B17" s="85"/>
-      <c r="C17" s="85"/>
-      <c r="D17" s="85"/>
-      <c r="E17" s="85"/>
-      <c r="F17" s="85"/>
-      <c r="G17" s="85"/>
-      <c r="H17" s="82"/>
-      <c r="I17" s="82"/>
-      <c r="J17" s="82"/>
-      <c r="K17" s="82"/>
-    </row>
-    <row r="18" spans="1:11" ht="18" x14ac:dyDescent="0.35">
-      <c r="A18" s="85"/>
-      <c r="B18" s="85"/>
-      <c r="C18" s="85"/>
-      <c r="D18" s="85"/>
-      <c r="E18" s="85"/>
-      <c r="F18" s="85"/>
-      <c r="G18" s="85"/>
-      <c r="H18" s="82"/>
-      <c r="I18" s="82"/>
-      <c r="J18" s="82"/>
-      <c r="K18" s="82"/>
-    </row>
-    <row r="19" spans="1:11" ht="18" x14ac:dyDescent="0.35">
-      <c r="A19" s="83" t="s">
-        <v>98</v>
-      </c>
-      <c r="B19" s="83"/>
-      <c r="C19" s="83"/>
-      <c r="D19" s="83"/>
-      <c r="E19" s="83"/>
-      <c r="F19" s="84"/>
-      <c r="G19" s="84"/>
-      <c r="H19" s="85"/>
-      <c r="I19" s="82"/>
-      <c r="J19" s="82"/>
-      <c r="K19" s="82"/>
-    </row>
-    <row r="20" spans="1:11" ht="18" x14ac:dyDescent="0.35">
-      <c r="A20" s="85" t="s">
-        <v>104</v>
-      </c>
-      <c r="B20" s="85"/>
-      <c r="C20" s="85"/>
-      <c r="D20" s="85"/>
-      <c r="E20" s="85"/>
-      <c r="F20" s="85"/>
-      <c r="G20" s="85"/>
-      <c r="H20" s="85"/>
-      <c r="I20" s="82"/>
-      <c r="J20" s="82"/>
-      <c r="K20" s="82"/>
-    </row>
-    <row r="21" spans="1:11" ht="18" x14ac:dyDescent="0.35">
-      <c r="A21" s="85" t="s">
-        <v>135</v>
-      </c>
-      <c r="B21" s="82"/>
-      <c r="C21" s="82"/>
-      <c r="D21" s="82"/>
-      <c r="E21" s="82"/>
-      <c r="F21" s="82"/>
-      <c r="G21" s="82"/>
-      <c r="H21" s="82"/>
-      <c r="I21" s="82"/>
-      <c r="J21" s="82"/>
-      <c r="K21" s="82"/>
+    <row r="9" spans="1:11" ht="15" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="131"/>
+      <c r="B9" s="131"/>
+      <c r="C9" s="131"/>
+      <c r="D9" s="131"/>
+      <c r="E9" s="131"/>
+      <c r="F9" s="131"/>
+      <c r="G9" s="131"/>
+      <c r="H9" s="131"/>
+      <c r="I9" s="131"/>
+      <c r="J9" s="131"/>
+      <c r="K9" s="131"/>
+    </row>
+    <row r="10" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A10" s="130" t="s">
+        <v>136</v>
+      </c>
+      <c r="B10" s="83"/>
+      <c r="C10" s="83"/>
+      <c r="D10" s="83"/>
+      <c r="E10" s="83"/>
+      <c r="F10" s="83"/>
+      <c r="G10" s="83"/>
+      <c r="H10" s="131"/>
+      <c r="I10" s="131"/>
+      <c r="J10" s="131"/>
+      <c r="K10" s="131"/>
+    </row>
+    <row r="11" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="127" t="s">
+        <v>137</v>
+      </c>
+      <c r="B11" s="127"/>
+      <c r="C11" s="127"/>
+      <c r="D11" s="127"/>
+      <c r="E11" s="127"/>
+      <c r="F11" s="127"/>
+      <c r="G11" s="127"/>
+      <c r="H11" s="131"/>
+      <c r="I11" s="131"/>
+      <c r="J11" s="131"/>
+      <c r="K11" s="131"/>
+    </row>
+    <row r="12" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="128" t="s">
+        <v>138</v>
+      </c>
+      <c r="B12" s="128"/>
+      <c r="C12" s="128"/>
+      <c r="D12" s="128"/>
+      <c r="E12" s="128"/>
+      <c r="F12" s="128"/>
+      <c r="G12" s="128"/>
+      <c r="H12" s="131"/>
+      <c r="I12" s="131"/>
+      <c r="J12" s="131"/>
+      <c r="K12" s="131"/>
+    </row>
+    <row r="13" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="129" t="s">
+        <v>139</v>
+      </c>
+      <c r="B13" s="129"/>
+      <c r="C13" s="129"/>
+      <c r="D13" s="129"/>
+      <c r="E13" s="129"/>
+      <c r="F13" s="129"/>
+      <c r="G13" s="129"/>
+      <c r="H13" s="131"/>
+      <c r="I13" s="131"/>
+      <c r="J13" s="131"/>
+      <c r="K13" s="131"/>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A14" s="131"/>
+      <c r="B14" s="131"/>
+      <c r="C14" s="131"/>
+      <c r="D14" s="131"/>
+      <c r="E14" s="131"/>
+      <c r="F14" s="131"/>
+      <c r="G14" s="131"/>
+      <c r="H14" s="131"/>
+      <c r="I14" s="131"/>
+      <c r="J14" s="131"/>
+      <c r="K14" s="131"/>
+    </row>
+    <row r="15" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="81" t="s">
+        <v>140</v>
+      </c>
+      <c r="B15" s="82"/>
+      <c r="C15" s="82"/>
+      <c r="D15" s="82"/>
+      <c r="E15" s="82"/>
+      <c r="F15" s="82"/>
+      <c r="G15" s="82"/>
+      <c r="H15" s="131"/>
+      <c r="I15" s="131"/>
+      <c r="J15" s="131"/>
+      <c r="K15" s="131"/>
+    </row>
+    <row r="16" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="83" t="s">
+        <v>141</v>
+      </c>
+      <c r="B16" s="83"/>
+      <c r="C16" s="83"/>
+      <c r="D16" s="83"/>
+      <c r="E16" s="83"/>
+      <c r="F16" s="83"/>
+      <c r="G16" s="83"/>
+      <c r="H16" s="131"/>
+      <c r="I16" s="131"/>
+      <c r="J16" s="131"/>
+      <c r="K16" s="131"/>
+    </row>
+    <row r="17" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="83" t="s">
+        <v>142</v>
+      </c>
+      <c r="B17" s="83"/>
+      <c r="C17" s="83"/>
+      <c r="D17" s="83"/>
+      <c r="E17" s="83"/>
+      <c r="F17" s="83"/>
+      <c r="G17" s="83"/>
+      <c r="H17" s="131"/>
+      <c r="I17" s="131"/>
+      <c r="J17" s="131"/>
+      <c r="K17" s="131"/>
+    </row>
+    <row r="18" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="83"/>
+      <c r="B18" s="83"/>
+      <c r="C18" s="83"/>
+      <c r="D18" s="83"/>
+      <c r="E18" s="83"/>
+      <c r="F18" s="83"/>
+      <c r="G18" s="83"/>
+      <c r="H18" s="131"/>
+      <c r="I18" s="131"/>
+      <c r="J18" s="131"/>
+      <c r="K18" s="131"/>
+    </row>
+    <row r="19" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="81" t="s">
+        <v>143</v>
+      </c>
+      <c r="B19" s="81"/>
+      <c r="C19" s="81"/>
+      <c r="D19" s="81"/>
+      <c r="E19" s="81"/>
+      <c r="F19" s="82"/>
+      <c r="G19" s="82"/>
+      <c r="H19" s="83"/>
+      <c r="I19" s="131"/>
+      <c r="J19" s="131"/>
+      <c r="K19" s="131"/>
+    </row>
+    <row r="20" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="83" t="s">
+        <v>144</v>
+      </c>
+      <c r="B20" s="83"/>
+      <c r="C20" s="83"/>
+      <c r="D20" s="83"/>
+      <c r="E20" s="83"/>
+      <c r="F20" s="83"/>
+      <c r="G20" s="83"/>
+      <c r="H20" s="83"/>
+      <c r="I20" s="131"/>
+      <c r="J20" s="131"/>
+      <c r="K20" s="131"/>
+    </row>
+    <row r="21" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="83" t="s">
+        <v>145</v>
+      </c>
+      <c r="B21" s="131"/>
+      <c r="C21" s="131"/>
+      <c r="D21" s="131"/>
+      <c r="E21" s="131"/>
+      <c r="F21" s="131"/>
+      <c r="G21" s="131"/>
+      <c r="H21" s="131"/>
+      <c r="I21" s="131"/>
+      <c r="J21" s="131"/>
+      <c r="K21" s="131"/>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A22" s="82"/>
-      <c r="B22" s="82"/>
-      <c r="C22" s="82"/>
-      <c r="D22" s="82"/>
-      <c r="E22" s="82"/>
-      <c r="F22" s="82"/>
-      <c r="G22" s="82"/>
-      <c r="H22" s="82"/>
-      <c r="I22" s="82"/>
-      <c r="J22" s="82"/>
-      <c r="K22" s="82"/>
-    </row>
-    <row r="23" spans="1:11" ht="18" x14ac:dyDescent="0.35">
-      <c r="A23" s="93" t="s">
-        <v>105</v>
-      </c>
-      <c r="B23" s="93"/>
-      <c r="C23" s="93"/>
-      <c r="D23" s="93"/>
-      <c r="E23" s="93"/>
-      <c r="F23" s="93"/>
-      <c r="G23" s="94"/>
-    </row>
-    <row r="24" spans="1:11" s="4" customFormat="1" ht="16.2" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="119"/>
-      <c r="B24" s="119"/>
-      <c r="C24" s="119"/>
-      <c r="D24" s="119"/>
-      <c r="E24" s="119"/>
-      <c r="F24" s="119"/>
-      <c r="G24" s="120"/>
-    </row>
-    <row r="25" spans="1:11" ht="18" x14ac:dyDescent="0.35">
-      <c r="A25" s="121" t="s">
-        <v>95</v>
-      </c>
-      <c r="B25" s="122"/>
-      <c r="C25" s="122"/>
-      <c r="D25" s="122"/>
-      <c r="E25" s="122"/>
-      <c r="F25" s="122"/>
-      <c r="G25" s="122"/>
+      <c r="A22" s="131"/>
+      <c r="B22" s="131"/>
+      <c r="C22" s="131"/>
+      <c r="D22" s="131"/>
+      <c r="E22" s="131"/>
+      <c r="F22" s="131"/>
+      <c r="G22" s="131"/>
+      <c r="H22" s="131"/>
+      <c r="I22" s="131"/>
+      <c r="J22" s="131"/>
+      <c r="K22" s="131"/>
+    </row>
+    <row r="23" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="91" t="s">
+        <v>146</v>
+      </c>
+      <c r="B23" s="91"/>
+      <c r="C23" s="91"/>
+      <c r="D23" s="91"/>
+      <c r="E23" s="91"/>
+      <c r="F23" s="91"/>
+      <c r="G23" s="92"/>
+    </row>
+    <row r="24" spans="1:11" ht="16.2" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="117"/>
+      <c r="B24" s="117"/>
+      <c r="C24" s="117"/>
+      <c r="D24" s="117"/>
+      <c r="E24" s="117"/>
+      <c r="F24" s="117"/>
+      <c r="G24" s="153"/>
+    </row>
+    <row r="25" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="118" t="s">
+        <v>147</v>
+      </c>
+      <c r="B25" s="119"/>
+      <c r="C25" s="119"/>
+      <c r="D25" s="119"/>
+      <c r="E25" s="119"/>
+      <c r="F25" s="119"/>
+      <c r="G25" s="119"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="5" scale="79" orientation="landscape" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+  <pageSetup paperSize="5" scale="79" orientation="landscape" horizontalDpi="0" verticalDpi="0"/>
   <headerFooter>
     <oddFooter>&amp;R&amp;P / &amp;N</oddFooter>
   </headerFooter>
